--- a/Inputs/Payment Overdue report shuddho.xlsx
+++ b/Inputs/Payment Overdue report shuddho.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21901"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sales_SalesRegister\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CGIT\Desktop\CBL Dealer Report\Inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{E9C6FD52-243D-4733-BA39-1D6932574F60}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D35000C-741A-48AD-B5D2-7F41D3584D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dealer Wise Payment Overdue19No" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4532" uniqueCount="838">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4534" uniqueCount="839">
   <si>
     <t># CONFIDENCE BATTERIES LIMITED #</t>
   </si>
@@ -2534,12 +2547,15 @@
   </si>
   <si>
     <t>M/S Arman Battery House</t>
+  </si>
+  <si>
+    <t>cr days</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -3085,9 +3101,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3125,7 +3141,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3231,7 +3247,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3373,18 +3389,21 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W571"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="12" width="9.140625" style="1"/>
+    <col min="14" max="14" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
@@ -3412,6 +3431,14 @@
         <v>4</v>
       </c>
     </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="N7" t="s">
+        <v>838</v>
+      </c>
+      <c r="O7" t="s">
+        <v>838</v>
+      </c>
+    </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
@@ -3479,7 +3506,7 @@
       <c r="V8" t="s">
         <v>26</v>
       </c>
-      <c r="W8" t="s">
+      <c r="W8" s="1" t="s">
         <v>27</v>
       </c>
     </row>
@@ -3550,7 +3577,7 @@
       <c r="V9">
         <v>-121450</v>
       </c>
-      <c r="W9">
+      <c r="W9" s="1">
         <v>2002528</v>
       </c>
     </row>
@@ -3621,7 +3648,7 @@
       <c r="V10">
         <v>-414458.25</v>
       </c>
-      <c r="W10">
+      <c r="W10" s="1">
         <v>615041.75</v>
       </c>
     </row>
@@ -3692,7 +3719,7 @@
       <c r="V11">
         <v>-235123.74</v>
       </c>
-      <c r="W11">
+      <c r="W11" s="1">
         <v>1564876.26</v>
       </c>
     </row>
@@ -3763,7 +3790,7 @@
       <c r="V12">
         <v>-128608.06</v>
       </c>
-      <c r="W12">
+      <c r="W12" s="1">
         <v>1421391.94</v>
       </c>
     </row>
@@ -3834,7 +3861,7 @@
       <c r="V13">
         <v>-186725.8</v>
       </c>
-      <c r="W13">
+      <c r="W13" s="1">
         <v>-186725.8</v>
       </c>
     </row>
@@ -3905,7 +3932,7 @@
       <c r="V14">
         <v>4620801.5</v>
       </c>
-      <c r="W14">
+      <c r="W14" s="1">
         <v>6230801.5</v>
       </c>
     </row>
@@ -3976,7 +4003,7 @@
       <c r="V15">
         <v>0</v>
       </c>
-      <c r="W15">
+      <c r="W15" s="1">
         <v>0</v>
       </c>
     </row>
@@ -4047,7 +4074,7 @@
       <c r="V16">
         <v>2899041</v>
       </c>
-      <c r="W16">
+      <c r="W16" s="1">
         <v>2899041</v>
       </c>
     </row>
@@ -4118,7 +4145,7 @@
       <c r="V17">
         <v>7210410</v>
       </c>
-      <c r="W17">
+      <c r="W17" s="1">
         <v>7210410</v>
       </c>
     </row>
@@ -4189,7 +4216,7 @@
       <c r="V18">
         <v>-242</v>
       </c>
-      <c r="W18">
+      <c r="W18" s="1">
         <v>-242</v>
       </c>
     </row>
@@ -4260,7 +4287,7 @@
       <c r="V19">
         <v>-13823</v>
       </c>
-      <c r="W19">
+      <c r="W19" s="1">
         <v>-13823</v>
       </c>
     </row>
@@ -4331,7 +4358,7 @@
       <c r="V20">
         <v>2592000</v>
       </c>
-      <c r="W20">
+      <c r="W20" s="1">
         <v>2592000</v>
       </c>
     </row>
@@ -4402,7 +4429,7 @@
       <c r="V21">
         <v>8801773.6500000004</v>
       </c>
-      <c r="W21">
+      <c r="W21" s="1">
         <v>30801773.649999999</v>
       </c>
     </row>
@@ -4473,7 +4500,7 @@
       <c r="V22">
         <v>275801.26</v>
       </c>
-      <c r="W22">
+      <c r="W22" s="1">
         <v>275801.26</v>
       </c>
     </row>
@@ -4544,7 +4571,7 @@
       <c r="V23">
         <v>-989037</v>
       </c>
-      <c r="W23">
+      <c r="W23" s="1">
         <v>-239037</v>
       </c>
     </row>
@@ -4615,7 +4642,7 @@
       <c r="V24">
         <v>371460.52</v>
       </c>
-      <c r="W24">
+      <c r="W24" s="1">
         <v>371460.52</v>
       </c>
     </row>
@@ -4686,7 +4713,7 @@
       <c r="V25">
         <v>2755213</v>
       </c>
-      <c r="W25">
+      <c r="W25" s="1">
         <v>5755213</v>
       </c>
     </row>
@@ -4757,7 +4784,7 @@
       <c r="V26">
         <v>0</v>
       </c>
-      <c r="W26">
+      <c r="W26" s="1">
         <v>0</v>
       </c>
     </row>
@@ -4828,7 +4855,7 @@
       <c r="V27">
         <v>275000</v>
       </c>
-      <c r="W27">
+      <c r="W27" s="1">
         <v>275000</v>
       </c>
     </row>
@@ -4899,7 +4926,7 @@
       <c r="V28">
         <v>666820</v>
       </c>
-      <c r="W28">
+      <c r="W28" s="1">
         <v>666820</v>
       </c>
     </row>
@@ -4970,7 +4997,7 @@
       <c r="V29">
         <v>-558000</v>
       </c>
-      <c r="W29">
+      <c r="W29" s="1">
         <v>-558000</v>
       </c>
     </row>
@@ -5041,7 +5068,7 @@
       <c r="V30">
         <v>1028945</v>
       </c>
-      <c r="W30">
+      <c r="W30" s="1">
         <v>1028945</v>
       </c>
     </row>
@@ -5112,7 +5139,7 @@
       <c r="V31">
         <v>1219979</v>
       </c>
-      <c r="W31">
+      <c r="W31" s="1">
         <v>1219979</v>
       </c>
     </row>
@@ -5183,7 +5210,7 @@
       <c r="V32">
         <v>1595770</v>
       </c>
-      <c r="W32">
+      <c r="W32" s="1">
         <v>1595770</v>
       </c>
     </row>
@@ -5254,7 +5281,7 @@
       <c r="V33">
         <v>1197453</v>
       </c>
-      <c r="W33">
+      <c r="W33" s="1">
         <v>1197453</v>
       </c>
     </row>
@@ -5325,7 +5352,7 @@
       <c r="V34">
         <v>161539.19</v>
       </c>
-      <c r="W34">
+      <c r="W34" s="1">
         <v>5347539.1900000004</v>
       </c>
     </row>
@@ -5396,7 +5423,7 @@
       <c r="V35">
         <v>1374875.29</v>
       </c>
-      <c r="W35">
+      <c r="W35" s="1">
         <v>4209875.29</v>
       </c>
     </row>
@@ -5467,7 +5494,7 @@
       <c r="V36">
         <v>-249223</v>
       </c>
-      <c r="W36">
+      <c r="W36" s="1">
         <v>1250777</v>
       </c>
     </row>
@@ -5538,7 +5565,7 @@
       <c r="V37">
         <v>-32744.23</v>
       </c>
-      <c r="W37">
+      <c r="W37" s="1">
         <v>4267255.7699999996</v>
       </c>
     </row>
@@ -5609,7 +5636,7 @@
       <c r="V38">
         <v>-3362727.18</v>
       </c>
-      <c r="W38">
+      <c r="W38" s="1">
         <v>-155227.18</v>
       </c>
     </row>
@@ -5680,7 +5707,7 @@
       <c r="V39">
         <v>-278852.07</v>
       </c>
-      <c r="W39">
+      <c r="W39" s="1">
         <v>121147.93</v>
       </c>
     </row>
@@ -5751,7 +5778,7 @@
       <c r="V40">
         <v>-1985832.29</v>
       </c>
-      <c r="W40">
+      <c r="W40" s="1">
         <v>279667.71000000002</v>
       </c>
     </row>
@@ -5822,7 +5849,7 @@
       <c r="V41">
         <v>-55519.29</v>
       </c>
-      <c r="W41">
+      <c r="W41" s="1">
         <v>449980.71</v>
       </c>
     </row>
@@ -5893,7 +5920,7 @@
       <c r="V42">
         <v>189572.91</v>
       </c>
-      <c r="W42">
+      <c r="W42" s="1">
         <v>189572.91</v>
       </c>
     </row>
@@ -5964,7 +5991,7 @@
       <c r="V43">
         <v>8094.96</v>
       </c>
-      <c r="W43">
+      <c r="W43" s="1">
         <v>8094.96</v>
       </c>
     </row>
@@ -6035,7 +6062,7 @@
       <c r="V44">
         <v>44823.05</v>
       </c>
-      <c r="W44">
+      <c r="W44" s="1">
         <v>44823.05</v>
       </c>
     </row>
@@ -6106,7 +6133,7 @@
       <c r="V45">
         <v>-656600.26</v>
       </c>
-      <c r="W45">
+      <c r="W45" s="1">
         <v>340066.74</v>
       </c>
     </row>
@@ -6177,7 +6204,7 @@
       <c r="V46">
         <v>0</v>
       </c>
-      <c r="W46">
+      <c r="W46" s="1">
         <v>0</v>
       </c>
     </row>
@@ -6248,7 +6275,7 @@
       <c r="V47">
         <v>19226</v>
       </c>
-      <c r="W47">
+      <c r="W47" s="1">
         <v>90176</v>
       </c>
     </row>
@@ -6319,7 +6346,7 @@
       <c r="V48">
         <v>6421510</v>
       </c>
-      <c r="W48">
+      <c r="W48" s="1">
         <v>9921510</v>
       </c>
     </row>
@@ -6390,7 +6417,7 @@
       <c r="V49">
         <v>97171</v>
       </c>
-      <c r="W49">
+      <c r="W49" s="1">
         <v>97171</v>
       </c>
     </row>
@@ -6461,7 +6488,7 @@
       <c r="V50">
         <v>-227024</v>
       </c>
-      <c r="W50">
+      <c r="W50" s="1">
         <v>372976</v>
       </c>
     </row>
@@ -6532,7 +6559,7 @@
       <c r="V51">
         <v>101276</v>
       </c>
-      <c r="W51">
+      <c r="W51" s="1">
         <v>101276</v>
       </c>
     </row>
@@ -6603,7 +6630,7 @@
       <c r="V52">
         <v>-13400</v>
       </c>
-      <c r="W52">
+      <c r="W52" s="1">
         <v>-13400</v>
       </c>
     </row>
@@ -6674,7 +6701,7 @@
       <c r="V53">
         <v>0</v>
       </c>
-      <c r="W53">
+      <c r="W53" s="1">
         <v>0</v>
       </c>
     </row>
@@ -6745,7 +6772,7 @@
       <c r="V54">
         <v>2262200</v>
       </c>
-      <c r="W54">
+      <c r="W54" s="1">
         <v>2262200</v>
       </c>
     </row>
@@ -6816,7 +6843,7 @@
       <c r="V55">
         <v>2096635</v>
       </c>
-      <c r="W55">
+      <c r="W55" s="1">
         <v>2096635</v>
       </c>
     </row>
@@ -6887,7 +6914,7 @@
       <c r="V56">
         <v>4560700</v>
       </c>
-      <c r="W56">
+      <c r="W56" s="1">
         <v>4560700</v>
       </c>
     </row>
@@ -6958,7 +6985,7 @@
       <c r="V57">
         <v>0</v>
       </c>
-      <c r="W57">
+      <c r="W57" s="1">
         <v>0</v>
       </c>
     </row>
@@ -7029,7 +7056,7 @@
       <c r="V58">
         <v>0</v>
       </c>
-      <c r="W58">
+      <c r="W58" s="1">
         <v>0</v>
       </c>
     </row>
@@ -7100,7 +7127,7 @@
       <c r="V59">
         <v>0</v>
       </c>
-      <c r="W59">
+      <c r="W59" s="1">
         <v>0</v>
       </c>
     </row>
@@ -7171,7 +7198,7 @@
       <c r="V60">
         <v>750000</v>
       </c>
-      <c r="W60">
+      <c r="W60" s="1">
         <v>750000</v>
       </c>
     </row>
@@ -7242,7 +7269,7 @@
       <c r="V61">
         <v>299421</v>
       </c>
-      <c r="W61">
+      <c r="W61" s="1">
         <v>299421</v>
       </c>
     </row>
@@ -7313,7 +7340,7 @@
       <c r="V62">
         <v>263705</v>
       </c>
-      <c r="W62">
+      <c r="W62" s="1">
         <v>263705</v>
       </c>
     </row>
@@ -7384,7 +7411,7 @@
       <c r="V63">
         <v>352516</v>
       </c>
-      <c r="W63">
+      <c r="W63" s="1">
         <v>352516</v>
       </c>
     </row>
@@ -7455,7 +7482,7 @@
       <c r="V64">
         <v>6356402</v>
       </c>
-      <c r="W64">
+      <c r="W64" s="1">
         <v>6356402</v>
       </c>
     </row>
@@ -7526,7 +7553,7 @@
       <c r="V65">
         <v>724900</v>
       </c>
-      <c r="W65">
+      <c r="W65" s="1">
         <v>724900</v>
       </c>
     </row>
@@ -7597,7 +7624,7 @@
       <c r="V66">
         <v>0</v>
       </c>
-      <c r="W66">
+      <c r="W66" s="1">
         <v>0</v>
       </c>
     </row>
@@ -7668,7 +7695,7 @@
       <c r="V67">
         <v>1069700</v>
       </c>
-      <c r="W67">
+      <c r="W67" s="1">
         <v>1069700</v>
       </c>
     </row>
@@ -7739,7 +7766,7 @@
       <c r="V68">
         <v>272656</v>
       </c>
-      <c r="W68">
+      <c r="W68" s="1">
         <v>272656</v>
       </c>
     </row>
@@ -7810,7 +7837,7 @@
       <c r="V69">
         <v>-0.08</v>
       </c>
-      <c r="W69">
+      <c r="W69" s="1">
         <v>-0.08</v>
       </c>
     </row>
@@ -7881,7 +7908,7 @@
       <c r="V70">
         <v>-224317.94</v>
       </c>
-      <c r="W70">
+      <c r="W70" s="1">
         <v>175682.06</v>
       </c>
     </row>
@@ -7952,7 +7979,7 @@
       <c r="V71">
         <v>338948.75</v>
       </c>
-      <c r="W71">
+      <c r="W71" s="1">
         <v>1526581.75</v>
       </c>
     </row>
@@ -8023,7 +8050,7 @@
       <c r="V72">
         <v>-31504.39</v>
       </c>
-      <c r="W72">
+      <c r="W72" s="1">
         <v>45558.61</v>
       </c>
     </row>
@@ -8094,7 +8121,7 @@
       <c r="V73">
         <v>-112469.26</v>
       </c>
-      <c r="W73">
+      <c r="W73" s="1">
         <v>-10911.26</v>
       </c>
     </row>
@@ -8165,7 +8192,7 @@
       <c r="V74">
         <v>-230014.82</v>
       </c>
-      <c r="W74">
+      <c r="W74" s="1">
         <v>494906.18</v>
       </c>
     </row>
@@ -8236,7 +8263,7 @@
       <c r="V75">
         <v>-257949.1</v>
       </c>
-      <c r="W75">
+      <c r="W75" s="1">
         <v>142050.9</v>
       </c>
     </row>
@@ -8307,7 +8334,7 @@
       <c r="V76">
         <v>-734976.66</v>
       </c>
-      <c r="W76">
+      <c r="W76" s="1">
         <v>-226555.66</v>
       </c>
     </row>
@@ -8378,7 +8405,7 @@
       <c r="V77">
         <v>-1140002.2</v>
       </c>
-      <c r="W77">
+      <c r="W77" s="1">
         <v>988747.8</v>
       </c>
     </row>
@@ -8449,7 +8476,7 @@
       <c r="V78">
         <v>-1470</v>
       </c>
-      <c r="W78">
+      <c r="W78" s="1">
         <v>-1470</v>
       </c>
     </row>
@@ -8520,7 +8547,7 @@
       <c r="V79">
         <v>-518403</v>
       </c>
-      <c r="W79">
+      <c r="W79" s="1">
         <v>-18403</v>
       </c>
     </row>
@@ -8591,7 +8618,7 @@
       <c r="V80">
         <v>0</v>
       </c>
-      <c r="W80">
+      <c r="W80" s="1">
         <v>0</v>
       </c>
     </row>
@@ -8662,7 +8689,7 @@
       <c r="V81">
         <v>50000</v>
       </c>
-      <c r="W81">
+      <c r="W81" s="1">
         <v>50000</v>
       </c>
     </row>
@@ -8733,7 +8760,7 @@
       <c r="V82">
         <v>213800</v>
       </c>
-      <c r="W82">
+      <c r="W82" s="1">
         <v>213800</v>
       </c>
     </row>
@@ -8804,7 +8831,7 @@
       <c r="V83">
         <v>7750</v>
       </c>
-      <c r="W83">
+      <c r="W83" s="1">
         <v>7750</v>
       </c>
     </row>
@@ -8875,7 +8902,7 @@
       <c r="V84">
         <v>0</v>
       </c>
-      <c r="W84">
+      <c r="W84" s="1">
         <v>0</v>
       </c>
     </row>
@@ -8946,7 +8973,7 @@
       <c r="V85">
         <v>-418000</v>
       </c>
-      <c r="W85">
+      <c r="W85" s="1">
         <v>-418000</v>
       </c>
     </row>
@@ -9017,7 +9044,7 @@
       <c r="V86">
         <v>0</v>
       </c>
-      <c r="W86">
+      <c r="W86" s="1">
         <v>0</v>
       </c>
     </row>
@@ -9088,7 +9115,7 @@
       <c r="V87">
         <v>558100</v>
       </c>
-      <c r="W87">
+      <c r="W87" s="1">
         <v>558100</v>
       </c>
     </row>
@@ -9159,7 +9186,7 @@
       <c r="V88">
         <v>301468</v>
       </c>
-      <c r="W88">
+      <c r="W88" s="1">
         <v>301468</v>
       </c>
     </row>
@@ -9230,7 +9257,7 @@
       <c r="V89">
         <v>0</v>
       </c>
-      <c r="W89">
+      <c r="W89" s="1">
         <v>0</v>
       </c>
     </row>
@@ -9301,7 +9328,7 @@
       <c r="V90">
         <v>148500</v>
       </c>
-      <c r="W90">
+      <c r="W90" s="1">
         <v>148500</v>
       </c>
     </row>
@@ -9372,7 +9399,7 @@
       <c r="V91">
         <v>439500</v>
       </c>
-      <c r="W91">
+      <c r="W91" s="1">
         <v>439500</v>
       </c>
     </row>
@@ -9443,7 +9470,7 @@
       <c r="V92">
         <v>11980</v>
       </c>
-      <c r="W92">
+      <c r="W92" s="1">
         <v>11980</v>
       </c>
     </row>
@@ -9514,7 +9541,7 @@
       <c r="V93">
         <v>41737.72</v>
       </c>
-      <c r="W93">
+      <c r="W93" s="1">
         <v>597237.72</v>
       </c>
     </row>
@@ -9585,7 +9612,7 @@
       <c r="V94">
         <v>331455.76</v>
       </c>
-      <c r="W94">
+      <c r="W94" s="1">
         <v>612455.76</v>
       </c>
     </row>
@@ -9656,7 +9683,7 @@
       <c r="V95">
         <v>230388.01</v>
       </c>
-      <c r="W95">
+      <c r="W95" s="1">
         <v>932888.01</v>
       </c>
     </row>
@@ -9727,7 +9754,7 @@
       <c r="V96">
         <v>155124.51999999999</v>
       </c>
-      <c r="W96">
+      <c r="W96" s="1">
         <v>155124.51999999999</v>
       </c>
     </row>
@@ -9798,7 +9825,7 @@
       <c r="V97">
         <v>-282367.61</v>
       </c>
-      <c r="W97">
+      <c r="W97" s="1">
         <v>1217632.3899999999</v>
       </c>
     </row>
@@ -9869,7 +9896,7 @@
       <c r="V98">
         <v>3506709.06</v>
       </c>
-      <c r="W98">
+      <c r="W98" s="1">
         <v>4506709.0599999996</v>
       </c>
     </row>
@@ -9940,7 +9967,7 @@
       <c r="V99">
         <v>-598788.38</v>
       </c>
-      <c r="W99">
+      <c r="W99" s="1">
         <v>86211.62</v>
       </c>
     </row>
@@ -10011,7 +10038,7 @@
       <c r="V100">
         <v>139267</v>
       </c>
-      <c r="W100">
+      <c r="W100" s="1">
         <v>139267</v>
       </c>
     </row>
@@ -10082,7 +10109,7 @@
       <c r="V101">
         <v>498571.3</v>
       </c>
-      <c r="W101">
+      <c r="W101" s="1">
         <v>498571.3</v>
       </c>
     </row>
@@ -10153,7 +10180,7 @@
       <c r="V102">
         <v>-1210</v>
       </c>
-      <c r="W102">
+      <c r="W102" s="1">
         <v>279790</v>
       </c>
     </row>
@@ -10224,7 +10251,7 @@
       <c r="V103">
         <v>3896.8</v>
       </c>
-      <c r="W103">
+      <c r="W103" s="1">
         <v>3896.8</v>
       </c>
     </row>
@@ -10295,7 +10322,7 @@
       <c r="V104">
         <v>52589</v>
       </c>
-      <c r="W104">
+      <c r="W104" s="1">
         <v>52589</v>
       </c>
     </row>
@@ -10366,7 +10393,7 @@
       <c r="V105">
         <v>104091</v>
       </c>
-      <c r="W105">
+      <c r="W105" s="1">
         <v>385091</v>
       </c>
     </row>
@@ -10437,7 +10464,7 @@
       <c r="V106">
         <v>28225</v>
       </c>
-      <c r="W106">
+      <c r="W106" s="1">
         <v>28225</v>
       </c>
     </row>
@@ -10508,7 +10535,7 @@
       <c r="V107">
         <v>266565</v>
       </c>
-      <c r="W107">
+      <c r="W107" s="1">
         <v>629065</v>
       </c>
     </row>
@@ -10579,7 +10606,7 @@
       <c r="V108">
         <v>4023288</v>
       </c>
-      <c r="W108">
+      <c r="W108" s="1">
         <v>4374538</v>
       </c>
     </row>
@@ -10650,7 +10677,7 @@
       <c r="V109">
         <v>1214611</v>
       </c>
-      <c r="W109">
+      <c r="W109" s="1">
         <v>1214611</v>
       </c>
     </row>
@@ -10721,7 +10748,7 @@
       <c r="V110">
         <v>-4442</v>
       </c>
-      <c r="W110">
+      <c r="W110" s="1">
         <v>-4442</v>
       </c>
     </row>
@@ -10792,7 +10819,7 @@
       <c r="V111">
         <v>0</v>
       </c>
-      <c r="W111">
+      <c r="W111" s="1">
         <v>0</v>
       </c>
     </row>
@@ -10863,7 +10890,7 @@
       <c r="V112">
         <v>2710200</v>
       </c>
-      <c r="W112">
+      <c r="W112" s="1">
         <v>2710200</v>
       </c>
     </row>
@@ -10934,7 +10961,7 @@
       <c r="V113">
         <v>0</v>
       </c>
-      <c r="W113">
+      <c r="W113" s="1">
         <v>0</v>
       </c>
     </row>
@@ -11005,7 +11032,7 @@
       <c r="V114">
         <v>0</v>
       </c>
-      <c r="W114">
+      <c r="W114" s="1">
         <v>0</v>
       </c>
     </row>
@@ -11076,7 +11103,7 @@
       <c r="V115">
         <v>0</v>
       </c>
-      <c r="W115">
+      <c r="W115" s="1">
         <v>0</v>
       </c>
     </row>
@@ -11147,7 +11174,7 @@
       <c r="V116">
         <v>890399</v>
       </c>
-      <c r="W116">
+      <c r="W116" s="1">
         <v>890399</v>
       </c>
     </row>
@@ -11218,7 +11245,7 @@
       <c r="V117">
         <v>56638</v>
       </c>
-      <c r="W117">
+      <c r="W117" s="1">
         <v>56638</v>
       </c>
     </row>
@@ -11289,7 +11316,7 @@
       <c r="V118">
         <v>-950127.81</v>
       </c>
-      <c r="W118">
+      <c r="W118" s="1">
         <v>2909272.19</v>
       </c>
     </row>
@@ -11360,7 +11387,7 @@
       <c r="V119">
         <v>2289931.71</v>
       </c>
-      <c r="W119">
+      <c r="W119" s="1">
         <v>3826514.71</v>
       </c>
     </row>
@@ -11431,7 +11458,7 @@
       <c r="V120">
         <v>-1030761.73</v>
       </c>
-      <c r="W120">
+      <c r="W120" s="1">
         <v>-79261.73</v>
       </c>
     </row>
@@ -11502,7 +11529,7 @@
       <c r="V121">
         <v>34450.31</v>
       </c>
-      <c r="W121">
+      <c r="W121" s="1">
         <v>34450.31</v>
       </c>
     </row>
@@ -11573,7 +11600,7 @@
       <c r="V122">
         <v>-106170.44</v>
       </c>
-      <c r="W122">
+      <c r="W122" s="1">
         <v>30829.56</v>
       </c>
     </row>
@@ -11644,7 +11671,7 @@
       <c r="V123">
         <v>-4942.32</v>
       </c>
-      <c r="W123">
+      <c r="W123" s="1">
         <v>346307.68</v>
       </c>
     </row>
@@ -11715,7 +11742,7 @@
       <c r="V124">
         <v>-30457.8</v>
       </c>
-      <c r="W124">
+      <c r="W124" s="1">
         <v>-1573.8</v>
       </c>
     </row>
@@ -11786,7 +11813,7 @@
       <c r="V125">
         <v>-34525</v>
       </c>
-      <c r="W125">
+      <c r="W125" s="1">
         <v>-34525</v>
       </c>
     </row>
@@ -11857,7 +11884,7 @@
       <c r="V126">
         <v>-28300.92</v>
       </c>
-      <c r="W126">
+      <c r="W126" s="1">
         <v>-3266.92</v>
       </c>
     </row>
@@ -11928,7 +11955,7 @@
       <c r="V127">
         <v>-92033.600000000006</v>
       </c>
-      <c r="W127">
+      <c r="W127" s="1">
         <v>-27103.599999999999</v>
       </c>
     </row>
@@ -11999,7 +12026,7 @@
       <c r="V128">
         <v>-25459</v>
       </c>
-      <c r="W128">
+      <c r="W128" s="1">
         <v>0</v>
       </c>
     </row>
@@ -12070,7 +12097,7 @@
       <c r="V129">
         <v>500</v>
       </c>
-      <c r="W129">
+      <c r="W129" s="1">
         <v>500</v>
       </c>
     </row>
@@ -12141,7 +12168,7 @@
       <c r="V130">
         <v>0</v>
       </c>
-      <c r="W130">
+      <c r="W130" s="1">
         <v>0</v>
       </c>
     </row>
@@ -12212,7 +12239,7 @@
       <c r="V131">
         <v>625147</v>
       </c>
-      <c r="W131">
+      <c r="W131" s="1">
         <v>625147</v>
       </c>
     </row>
@@ -12283,7 +12310,7 @@
       <c r="V132">
         <v>0</v>
       </c>
-      <c r="W132">
+      <c r="W132" s="1">
         <v>0</v>
       </c>
     </row>
@@ -12354,7 +12381,7 @@
       <c r="V133">
         <v>-5000</v>
       </c>
-      <c r="W133">
+      <c r="W133" s="1">
         <v>-5000</v>
       </c>
     </row>
@@ -12425,7 +12452,7 @@
       <c r="V134">
         <v>-282600</v>
       </c>
-      <c r="W134">
+      <c r="W134" s="1">
         <v>-1600</v>
       </c>
     </row>
@@ -12496,7 +12523,7 @@
       <c r="V135">
         <v>192280</v>
       </c>
-      <c r="W135">
+      <c r="W135" s="1">
         <v>192280</v>
       </c>
     </row>
@@ -12567,7 +12594,7 @@
       <c r="V136">
         <v>356200</v>
       </c>
-      <c r="W136">
+      <c r="W136" s="1">
         <v>356200</v>
       </c>
     </row>
@@ -12638,7 +12665,7 @@
       <c r="V137">
         <v>0</v>
       </c>
-      <c r="W137">
+      <c r="W137" s="1">
         <v>0</v>
       </c>
     </row>
@@ -12709,7 +12736,7 @@
       <c r="V138">
         <v>183772</v>
       </c>
-      <c r="W138">
+      <c r="W138" s="1">
         <v>183772</v>
       </c>
     </row>
@@ -12780,7 +12807,7 @@
       <c r="V139">
         <v>0</v>
       </c>
-      <c r="W139">
+      <c r="W139" s="1">
         <v>0</v>
       </c>
     </row>
@@ -12851,7 +12878,7 @@
       <c r="V140">
         <v>15165</v>
       </c>
-      <c r="W140">
+      <c r="W140" s="1">
         <v>15165</v>
       </c>
     </row>
@@ -12922,7 +12949,7 @@
       <c r="V141">
         <v>-568243.53</v>
       </c>
-      <c r="W141">
+      <c r="W141" s="1">
         <v>-97743.53</v>
       </c>
     </row>
@@ -12993,7 +13020,7 @@
       <c r="V142">
         <v>1884250.24</v>
       </c>
-      <c r="W142">
+      <c r="W142" s="1">
         <v>1884250.24</v>
       </c>
     </row>
@@ -13064,7 +13091,7 @@
       <c r="V143">
         <v>-65530.080000000002</v>
       </c>
-      <c r="W143">
+      <c r="W143" s="1">
         <v>186052.92</v>
       </c>
     </row>
@@ -13135,7 +13162,7 @@
       <c r="V144">
         <v>0</v>
       </c>
-      <c r="W144">
+      <c r="W144" s="1">
         <v>0</v>
       </c>
     </row>
@@ -13206,7 +13233,7 @@
       <c r="V145">
         <v>0</v>
       </c>
-      <c r="W145">
+      <c r="W145" s="1">
         <v>0</v>
       </c>
     </row>
@@ -13277,7 +13304,7 @@
       <c r="V146">
         <v>-19574</v>
       </c>
-      <c r="W146">
+      <c r="W146" s="1">
         <v>-19574</v>
       </c>
     </row>
@@ -13348,7 +13375,7 @@
       <c r="V147">
         <v>354447</v>
       </c>
-      <c r="W147">
+      <c r="W147" s="1">
         <v>562947</v>
       </c>
     </row>
@@ -13419,7 +13446,7 @@
       <c r="V148">
         <v>64139</v>
       </c>
-      <c r="W148">
+      <c r="W148" s="1">
         <v>64139</v>
       </c>
     </row>
@@ -13490,7 +13517,7 @@
       <c r="V149">
         <v>317343</v>
       </c>
-      <c r="W149">
+      <c r="W149" s="1">
         <v>317343</v>
       </c>
     </row>
@@ -13561,7 +13588,7 @@
       <c r="V150">
         <v>287531.95</v>
       </c>
-      <c r="W150">
+      <c r="W150" s="1">
         <v>287531.95</v>
       </c>
     </row>
@@ -13632,7 +13659,7 @@
       <c r="V151">
         <v>186321.63</v>
       </c>
-      <c r="W151">
+      <c r="W151" s="1">
         <v>186321.63</v>
       </c>
     </row>
@@ -13703,7 +13730,7 @@
       <c r="V152">
         <v>-950657.22</v>
       </c>
-      <c r="W152">
+      <c r="W152" s="1">
         <v>-450657.22</v>
       </c>
     </row>
@@ -13774,7 +13801,7 @@
       <c r="V153">
         <v>66352.679999999993</v>
       </c>
-      <c r="W153">
+      <c r="W153" s="1">
         <v>66352.679999999993</v>
       </c>
     </row>
@@ -13845,7 +13872,7 @@
       <c r="V154">
         <v>813390.3</v>
       </c>
-      <c r="W154">
+      <c r="W154" s="1">
         <v>813390.3</v>
       </c>
     </row>
@@ -13916,7 +13943,7 @@
       <c r="V155">
         <v>5613200</v>
       </c>
-      <c r="W155">
+      <c r="W155" s="1">
         <v>5613200</v>
       </c>
     </row>
@@ -13987,7 +14014,7 @@
       <c r="V156">
         <v>1694295</v>
       </c>
-      <c r="W156">
+      <c r="W156" s="1">
         <v>1694295</v>
       </c>
     </row>
@@ -14058,7 +14085,7 @@
       <c r="V157">
         <v>10500</v>
       </c>
-      <c r="W157">
+      <c r="W157" s="1">
         <v>10500</v>
       </c>
     </row>
@@ -14129,7 +14156,7 @@
       <c r="V158">
         <v>0</v>
       </c>
-      <c r="W158">
+      <c r="W158" s="1">
         <v>0</v>
       </c>
     </row>
@@ -14200,7 +14227,7 @@
       <c r="V159">
         <v>0</v>
       </c>
-      <c r="W159">
+      <c r="W159" s="1">
         <v>0</v>
       </c>
     </row>
@@ -14271,7 +14298,7 @@
       <c r="V160">
         <v>-6800</v>
       </c>
-      <c r="W160">
+      <c r="W160" s="1">
         <v>-6800</v>
       </c>
     </row>
@@ -14342,7 +14369,7 @@
       <c r="V161">
         <v>-301</v>
       </c>
-      <c r="W161">
+      <c r="W161" s="1">
         <v>-301</v>
       </c>
     </row>
@@ -14413,7 +14440,7 @@
       <c r="V162">
         <v>5255066.1500000004</v>
       </c>
-      <c r="W162">
+      <c r="W162" s="1">
         <v>8882374.1500000004</v>
       </c>
     </row>
@@ -14484,7 +14511,7 @@
       <c r="V163">
         <v>3415060.83</v>
       </c>
-      <c r="W163">
+      <c r="W163" s="1">
         <v>7799060.8300000001</v>
       </c>
     </row>
@@ -14555,7 +14582,7 @@
       <c r="V164">
         <v>39532.07</v>
       </c>
-      <c r="W164">
+      <c r="W164" s="1">
         <v>39532.07</v>
       </c>
     </row>
@@ -14626,7 +14653,7 @@
       <c r="V165">
         <v>734794</v>
       </c>
-      <c r="W165">
+      <c r="W165" s="1">
         <v>2479932</v>
       </c>
     </row>
@@ -14697,7 +14724,7 @@
       <c r="V166">
         <v>1718561.82</v>
       </c>
-      <c r="W166">
+      <c r="W166" s="1">
         <v>4718561.82</v>
       </c>
     </row>
@@ -14768,7 +14795,7 @@
       <c r="V167">
         <v>120314.71</v>
       </c>
-      <c r="W167">
+      <c r="W167" s="1">
         <v>1394314.71</v>
       </c>
     </row>
@@ -14839,7 +14866,7 @@
       <c r="V168">
         <v>344378</v>
       </c>
-      <c r="W168">
+      <c r="W168" s="1">
         <v>2631328</v>
       </c>
     </row>
@@ -14910,7 +14937,7 @@
       <c r="V169">
         <v>937847</v>
       </c>
-      <c r="W169">
+      <c r="W169" s="1">
         <v>1348847</v>
       </c>
     </row>
@@ -14981,7 +15008,7 @@
       <c r="V170">
         <v>-11778</v>
       </c>
-      <c r="W170">
+      <c r="W170" s="1">
         <v>-11778</v>
       </c>
     </row>
@@ -15052,7 +15079,7 @@
       <c r="V171">
         <v>0</v>
       </c>
-      <c r="W171">
+      <c r="W171" s="1">
         <v>0</v>
       </c>
     </row>
@@ -15123,7 +15150,7 @@
       <c r="V172">
         <v>0</v>
       </c>
-      <c r="W172">
+      <c r="W172" s="1">
         <v>0</v>
       </c>
     </row>
@@ -15194,7 +15221,7 @@
       <c r="V173">
         <v>0</v>
       </c>
-      <c r="W173">
+      <c r="W173" s="1">
         <v>0</v>
       </c>
     </row>
@@ -15265,7 +15292,7 @@
       <c r="V174">
         <v>0</v>
       </c>
-      <c r="W174">
+      <c r="W174" s="1">
         <v>0</v>
       </c>
     </row>
@@ -15336,7 +15363,7 @@
       <c r="V175">
         <v>-10000</v>
       </c>
-      <c r="W175">
+      <c r="W175" s="1">
         <v>-10000</v>
       </c>
     </row>
@@ -15407,7 +15434,7 @@
       <c r="V176">
         <v>-6438088.2000000002</v>
       </c>
-      <c r="W176">
+      <c r="W176" s="1">
         <v>2061911.8</v>
       </c>
     </row>
@@ -15478,7 +15505,7 @@
       <c r="V177">
         <v>-3535897.85</v>
       </c>
-      <c r="W177">
+      <c r="W177" s="1">
         <v>-1535897.85</v>
       </c>
     </row>
@@ -15549,7 +15576,7 @@
       <c r="V178">
         <v>-41424.65</v>
       </c>
-      <c r="W178">
+      <c r="W178" s="1">
         <v>-41424.65</v>
       </c>
     </row>
@@ -15620,7 +15647,7 @@
       <c r="V179">
         <v>-545532.91</v>
       </c>
-      <c r="W179">
+      <c r="W179" s="1">
         <v>0.09</v>
       </c>
     </row>
@@ -15691,7 +15718,7 @@
       <c r="V180">
         <v>-286672.37</v>
       </c>
-      <c r="W180">
+      <c r="W180" s="1">
         <v>64577.63</v>
       </c>
     </row>
@@ -15762,7 +15789,7 @@
       <c r="V181">
         <v>-136532.10999999999</v>
       </c>
-      <c r="W181">
+      <c r="W181" s="1">
         <v>-61107.11</v>
       </c>
     </row>
@@ -15833,7 +15860,7 @@
       <c r="V182">
         <v>0.2</v>
       </c>
-      <c r="W182">
+      <c r="W182" s="1">
         <v>0.2</v>
       </c>
     </row>
@@ -15904,7 +15931,7 @@
       <c r="V183">
         <v>-198132.4</v>
       </c>
-      <c r="W183">
+      <c r="W183" s="1">
         <v>-22319.4</v>
       </c>
     </row>
@@ -15975,7 +16002,7 @@
       <c r="V184">
         <v>-249296.33</v>
       </c>
-      <c r="W184">
+      <c r="W184" s="1">
         <v>-98096.33</v>
       </c>
     </row>
@@ -16046,7 +16073,7 @@
       <c r="V185">
         <v>-2555821.75</v>
       </c>
-      <c r="W185">
+      <c r="W185" s="1">
         <v>-55821.75</v>
       </c>
     </row>
@@ -16117,7 +16144,7 @@
       <c r="V186">
         <v>450</v>
       </c>
-      <c r="W186">
+      <c r="W186" s="1">
         <v>450</v>
       </c>
     </row>
@@ -16188,7 +16215,7 @@
       <c r="V187">
         <v>-170908.4</v>
       </c>
-      <c r="W187">
+      <c r="W187" s="1">
         <v>38704.6</v>
       </c>
     </row>
@@ -16259,7 +16286,7 @@
       <c r="V188">
         <v>-4949.1000000000004</v>
       </c>
-      <c r="W188">
+      <c r="W188" s="1">
         <v>-4949.1000000000004</v>
       </c>
     </row>
@@ -16330,7 +16357,7 @@
       <c r="V189">
         <v>-62850.38</v>
       </c>
-      <c r="W189">
+      <c r="W189" s="1">
         <v>-0.38</v>
       </c>
     </row>
@@ -16401,7 +16428,7 @@
       <c r="V190">
         <v>-2902683</v>
       </c>
-      <c r="W190">
+      <c r="W190" s="1">
         <v>-1902683</v>
       </c>
     </row>
@@ -16472,7 +16499,7 @@
       <c r="V191">
         <v>1450225</v>
       </c>
-      <c r="W191">
+      <c r="W191" s="1">
         <v>1450225</v>
       </c>
     </row>
@@ -16543,7 +16570,7 @@
       <c r="V192">
         <v>-949924</v>
       </c>
-      <c r="W192">
+      <c r="W192" s="1">
         <v>-177174</v>
       </c>
     </row>
@@ -16614,7 +16641,7 @@
       <c r="V193">
         <v>-126696</v>
       </c>
-      <c r="W193">
+      <c r="W193" s="1">
         <v>911754</v>
       </c>
     </row>
@@ -16685,7 +16712,7 @@
       <c r="V194">
         <v>-520461</v>
       </c>
-      <c r="W194">
+      <c r="W194" s="1">
         <v>487047</v>
       </c>
     </row>
@@ -16756,7 +16783,7 @@
       <c r="V195">
         <v>-35660</v>
       </c>
-      <c r="W195">
+      <c r="W195" s="1">
         <v>-35660</v>
       </c>
     </row>
@@ -16827,7 +16854,7 @@
       <c r="V196">
         <v>3562808</v>
       </c>
-      <c r="W196">
+      <c r="W196" s="1">
         <v>3562808</v>
       </c>
     </row>
@@ -16898,7 +16925,7 @@
       <c r="V197">
         <v>-18294</v>
       </c>
-      <c r="W197">
+      <c r="W197" s="1">
         <v>-18294</v>
       </c>
     </row>
@@ -16969,7 +16996,7 @@
       <c r="V198">
         <v>0</v>
       </c>
-      <c r="W198">
+      <c r="W198" s="1">
         <v>0</v>
       </c>
     </row>
@@ -17040,7 +17067,7 @@
       <c r="V199">
         <v>0</v>
       </c>
-      <c r="W199">
+      <c r="W199" s="1">
         <v>0</v>
       </c>
     </row>
@@ -17111,7 +17138,7 @@
       <c r="V200">
         <v>0</v>
       </c>
-      <c r="W200">
+      <c r="W200" s="1">
         <v>0</v>
       </c>
     </row>
@@ -17182,7 +17209,7 @@
       <c r="V201">
         <v>539</v>
       </c>
-      <c r="W201">
+      <c r="W201" s="1">
         <v>539</v>
       </c>
     </row>
@@ -17253,7 +17280,7 @@
       <c r="V202">
         <v>-3174</v>
       </c>
-      <c r="W202">
+      <c r="W202" s="1">
         <v>-3174</v>
       </c>
     </row>
@@ -17324,7 +17351,7 @@
       <c r="V203">
         <v>143903</v>
       </c>
-      <c r="W203">
+      <c r="W203" s="1">
         <v>143903</v>
       </c>
     </row>
@@ -17395,7 +17422,7 @@
       <c r="V204">
         <v>2040171</v>
       </c>
-      <c r="W204">
+      <c r="W204" s="1">
         <v>2040171</v>
       </c>
     </row>
@@ -17466,7 +17493,7 @@
       <c r="V205">
         <v>32650</v>
       </c>
-      <c r="W205">
+      <c r="W205" s="1">
         <v>32650</v>
       </c>
     </row>
@@ -17537,7 +17564,7 @@
       <c r="V206">
         <v>308550</v>
       </c>
-      <c r="W206">
+      <c r="W206" s="1">
         <v>308550</v>
       </c>
     </row>
@@ -17608,7 +17635,7 @@
       <c r="V207">
         <v>145000</v>
       </c>
-      <c r="W207">
+      <c r="W207" s="1">
         <v>145000</v>
       </c>
     </row>
@@ -17679,7 +17706,7 @@
       <c r="V208">
         <v>2888975</v>
       </c>
-      <c r="W208">
+      <c r="W208" s="1">
         <v>2888975</v>
       </c>
     </row>
@@ -17750,7 +17777,7 @@
       <c r="V209">
         <v>-251500</v>
       </c>
-      <c r="W209">
+      <c r="W209" s="1">
         <v>-251500</v>
       </c>
     </row>
@@ -17821,7 +17848,7 @@
       <c r="V210">
         <v>2834359</v>
       </c>
-      <c r="W210">
+      <c r="W210" s="1">
         <v>2834359</v>
       </c>
     </row>
@@ -17892,7 +17919,7 @@
       <c r="V211">
         <v>-147800</v>
       </c>
-      <c r="W211">
+      <c r="W211" s="1">
         <v>-147800</v>
       </c>
     </row>
@@ -17963,7 +17990,7 @@
       <c r="V212">
         <v>580500</v>
       </c>
-      <c r="W212">
+      <c r="W212" s="1">
         <v>580500</v>
       </c>
     </row>
@@ -18034,7 +18061,7 @@
       <c r="V213">
         <v>-447386.75</v>
       </c>
-      <c r="W213">
+      <c r="W213" s="1">
         <v>874113.25</v>
       </c>
     </row>
@@ -18105,7 +18132,7 @@
       <c r="V214">
         <v>-2864944.32</v>
       </c>
-      <c r="W214">
+      <c r="W214" s="1">
         <v>1396055.68</v>
       </c>
     </row>
@@ -18176,7 +18203,7 @@
       <c r="V215">
         <v>11930</v>
       </c>
-      <c r="W215">
+      <c r="W215" s="1">
         <v>11930</v>
       </c>
     </row>
@@ -18247,7 +18274,7 @@
       <c r="V216">
         <v>-250950</v>
       </c>
-      <c r="W216">
+      <c r="W216" s="1">
         <v>1116100</v>
       </c>
     </row>
@@ -18318,7 +18345,7 @@
       <c r="V217">
         <v>0</v>
       </c>
-      <c r="W217">
+      <c r="W217" s="1">
         <v>0</v>
       </c>
     </row>
@@ -18389,7 +18416,7 @@
       <c r="V218">
         <v>-658368</v>
       </c>
-      <c r="W218">
+      <c r="W218" s="1">
         <v>47132</v>
       </c>
     </row>
@@ -18460,7 +18487,7 @@
       <c r="V219">
         <v>-476480</v>
       </c>
-      <c r="W219">
+      <c r="W219" s="1">
         <v>-125230</v>
       </c>
     </row>
@@ -18531,7 +18558,7 @@
       <c r="V220">
         <v>0</v>
       </c>
-      <c r="W220">
+      <c r="W220" s="1">
         <v>0</v>
       </c>
     </row>
@@ -18602,7 +18629,7 @@
       <c r="V221">
         <v>2525700</v>
       </c>
-      <c r="W221">
+      <c r="W221" s="1">
         <v>2525700</v>
       </c>
     </row>
@@ -18673,7 +18700,7 @@
       <c r="V222">
         <v>122000</v>
       </c>
-      <c r="W222">
+      <c r="W222" s="1">
         <v>122000</v>
       </c>
     </row>
@@ -18744,7 +18771,7 @@
       <c r="V223">
         <v>1297790</v>
       </c>
-      <c r="W223">
+      <c r="W223" s="1">
         <v>1297790</v>
       </c>
     </row>
@@ -18815,7 +18842,7 @@
       <c r="V224">
         <v>161000</v>
       </c>
-      <c r="W224">
+      <c r="W224" s="1">
         <v>161000</v>
       </c>
     </row>
@@ -18886,7 +18913,7 @@
       <c r="V225">
         <v>358500</v>
       </c>
-      <c r="W225">
+      <c r="W225" s="1">
         <v>358500</v>
       </c>
     </row>
@@ -18957,7 +18984,7 @@
       <c r="V226">
         <v>-48036</v>
       </c>
-      <c r="W226">
+      <c r="W226" s="1">
         <v>-48036</v>
       </c>
     </row>
@@ -19028,7 +19055,7 @@
       <c r="V227">
         <v>-225.38</v>
       </c>
-      <c r="W227">
+      <c r="W227" s="1">
         <v>-225.38</v>
       </c>
     </row>
@@ -19099,7 +19126,7 @@
       <c r="V228">
         <v>29563.71</v>
       </c>
-      <c r="W228">
+      <c r="W228" s="1">
         <v>1366563.71</v>
       </c>
     </row>
@@ -19170,7 +19197,7 @@
       <c r="V229">
         <v>1313982.5</v>
       </c>
-      <c r="W229">
+      <c r="W229" s="1">
         <v>1313982.5</v>
       </c>
     </row>
@@ -19241,7 +19268,7 @@
       <c r="V230">
         <v>-114208.46</v>
       </c>
-      <c r="W230">
+      <c r="W230" s="1">
         <v>96541.54</v>
       </c>
     </row>
@@ -19312,7 +19339,7 @@
       <c r="V231">
         <v>2575</v>
       </c>
-      <c r="W231">
+      <c r="W231" s="1">
         <v>2575</v>
       </c>
     </row>
@@ -19383,7 +19410,7 @@
       <c r="V232">
         <v>-519499</v>
       </c>
-      <c r="W232">
+      <c r="W232" s="1">
         <v>430501</v>
       </c>
     </row>
@@ -19454,7 +19481,7 @@
       <c r="V233">
         <v>-491960.32000000001</v>
       </c>
-      <c r="W233">
+      <c r="W233" s="1">
         <v>226539.68</v>
       </c>
     </row>
@@ -19525,7 +19552,7 @@
       <c r="V234">
         <v>17184</v>
       </c>
-      <c r="W234">
+      <c r="W234" s="1">
         <v>496684</v>
       </c>
     </row>
@@ -19596,7 +19623,7 @@
       <c r="V235">
         <v>-404480</v>
       </c>
-      <c r="W235">
+      <c r="W235" s="1">
         <v>6520</v>
       </c>
     </row>
@@ -19667,7 +19694,7 @@
       <c r="V236">
         <v>-5620</v>
       </c>
-      <c r="W236">
+      <c r="W236" s="1">
         <v>-5620</v>
       </c>
     </row>
@@ -19738,7 +19765,7 @@
       <c r="V237">
         <v>0</v>
       </c>
-      <c r="W237">
+      <c r="W237" s="1">
         <v>0</v>
       </c>
     </row>
@@ -19809,7 +19836,7 @@
       <c r="V238">
         <v>-6000</v>
       </c>
-      <c r="W238">
+      <c r="W238" s="1">
         <v>-6000</v>
       </c>
     </row>
@@ -19880,7 +19907,7 @@
       <c r="V239">
         <v>0</v>
       </c>
-      <c r="W239">
+      <c r="W239" s="1">
         <v>0</v>
       </c>
     </row>
@@ -19951,7 +19978,7 @@
       <c r="V240">
         <v>-13400</v>
       </c>
-      <c r="W240">
+      <c r="W240" s="1">
         <v>-13400</v>
       </c>
     </row>
@@ -20022,7 +20049,7 @@
       <c r="V241">
         <v>0</v>
       </c>
-      <c r="W241">
+      <c r="W241" s="1">
         <v>0</v>
       </c>
     </row>
@@ -20093,7 +20120,7 @@
       <c r="V242">
         <v>514293</v>
       </c>
-      <c r="W242">
+      <c r="W242" s="1">
         <v>935793</v>
       </c>
     </row>
@@ -20164,7 +20191,7 @@
       <c r="V243">
         <v>-1250</v>
       </c>
-      <c r="W243">
+      <c r="W243" s="1">
         <v>-1250</v>
       </c>
     </row>
@@ -20235,7 +20262,7 @@
       <c r="V244">
         <v>11839</v>
       </c>
-      <c r="W244">
+      <c r="W244" s="1">
         <v>11839</v>
       </c>
     </row>
@@ -20306,7 +20333,7 @@
       <c r="V245">
         <v>127630</v>
       </c>
-      <c r="W245">
+      <c r="W245" s="1">
         <v>127630</v>
       </c>
     </row>
@@ -20377,7 +20404,7 @@
       <c r="V246">
         <v>13000</v>
       </c>
-      <c r="W246">
+      <c r="W246" s="1">
         <v>13000</v>
       </c>
     </row>
@@ -20448,7 +20475,7 @@
       <c r="V247">
         <v>2575468</v>
       </c>
-      <c r="W247">
+      <c r="W247" s="1">
         <v>2575468</v>
       </c>
     </row>
@@ -20519,7 +20546,7 @@
       <c r="V248">
         <v>25940</v>
       </c>
-      <c r="W248">
+      <c r="W248" s="1">
         <v>25940</v>
       </c>
     </row>
@@ -20590,7 +20617,7 @@
       <c r="V249">
         <v>86400</v>
       </c>
-      <c r="W249">
+      <c r="W249" s="1">
         <v>86400</v>
       </c>
     </row>
@@ -20661,7 +20688,7 @@
       <c r="V250">
         <v>180500</v>
       </c>
-      <c r="W250">
+      <c r="W250" s="1">
         <v>180500</v>
       </c>
     </row>
@@ -20732,7 +20759,7 @@
       <c r="V251">
         <v>111800</v>
       </c>
-      <c r="W251">
+      <c r="W251" s="1">
         <v>111800</v>
       </c>
     </row>
@@ -20803,7 +20830,7 @@
       <c r="V252">
         <v>2012</v>
       </c>
-      <c r="W252">
+      <c r="W252" s="1">
         <v>2012</v>
       </c>
     </row>
@@ -20874,7 +20901,7 @@
       <c r="V253">
         <v>24500</v>
       </c>
-      <c r="W253">
+      <c r="W253" s="1">
         <v>24500</v>
       </c>
     </row>
@@ -20945,7 +20972,7 @@
       <c r="V254">
         <v>-2000</v>
       </c>
-      <c r="W254">
+      <c r="W254" s="1">
         <v>-2000</v>
       </c>
     </row>
@@ -21016,7 +21043,7 @@
       <c r="V255">
         <v>172500</v>
       </c>
-      <c r="W255">
+      <c r="W255" s="1">
         <v>172500</v>
       </c>
     </row>
@@ -21087,7 +21114,7 @@
       <c r="V256">
         <v>124000</v>
       </c>
-      <c r="W256">
+      <c r="W256" s="1">
         <v>124000</v>
       </c>
     </row>
@@ -21158,7 +21185,7 @@
       <c r="V257">
         <v>174999</v>
       </c>
-      <c r="W257">
+      <c r="W257" s="1">
         <v>174999</v>
       </c>
     </row>
@@ -21229,7 +21256,7 @@
       <c r="V258">
         <v>32000</v>
       </c>
-      <c r="W258">
+      <c r="W258" s="1">
         <v>32000</v>
       </c>
     </row>
@@ -21300,7 +21327,7 @@
       <c r="V259">
         <v>2916</v>
       </c>
-      <c r="W259">
+      <c r="W259" s="1">
         <v>2916</v>
       </c>
     </row>
@@ -21371,7 +21398,7 @@
       <c r="V260">
         <v>0</v>
       </c>
-      <c r="W260">
+      <c r="W260" s="1">
         <v>0</v>
       </c>
     </row>
@@ -21442,7 +21469,7 @@
       <c r="V261">
         <v>-1005348.31</v>
       </c>
-      <c r="W261">
+      <c r="W261" s="1">
         <v>179651.69</v>
       </c>
     </row>
@@ -21513,7 +21540,7 @@
       <c r="V262">
         <v>449296.4</v>
       </c>
-      <c r="W262">
+      <c r="W262" s="1">
         <v>449296.4</v>
       </c>
     </row>
@@ -21584,7 +21611,7 @@
       <c r="V263">
         <v>-142143.6</v>
       </c>
-      <c r="W263">
+      <c r="W263" s="1">
         <v>-1643.6</v>
       </c>
     </row>
@@ -21655,7 +21682,7 @@
       <c r="V264">
         <v>-140505</v>
       </c>
-      <c r="W264">
+      <c r="W264" s="1">
         <v>-5</v>
       </c>
     </row>
@@ -21726,7 +21753,7 @@
       <c r="V265">
         <v>-134652</v>
       </c>
-      <c r="W265">
+      <c r="W265" s="1">
         <v>5848</v>
       </c>
     </row>
@@ -21797,7 +21824,7 @@
       <c r="V266">
         <v>66227</v>
       </c>
-      <c r="W266">
+      <c r="W266" s="1">
         <v>66227</v>
       </c>
     </row>
@@ -21868,7 +21895,7 @@
       <c r="V267">
         <v>212406</v>
       </c>
-      <c r="W267">
+      <c r="W267" s="1">
         <v>212406</v>
       </c>
     </row>
@@ -21939,7 +21966,7 @@
       <c r="V268">
         <v>974958</v>
       </c>
-      <c r="W268">
+      <c r="W268" s="1">
         <v>974958</v>
       </c>
     </row>
@@ -22010,7 +22037,7 @@
       <c r="V269">
         <v>263900</v>
       </c>
-      <c r="W269">
+      <c r="W269" s="1">
         <v>263900</v>
       </c>
     </row>
@@ -22081,7 +22108,7 @@
       <c r="V270">
         <v>0</v>
       </c>
-      <c r="W270">
+      <c r="W270" s="1">
         <v>0</v>
       </c>
     </row>
@@ -22152,7 +22179,7 @@
       <c r="V271">
         <v>72000</v>
       </c>
-      <c r="W271">
+      <c r="W271" s="1">
         <v>72000</v>
       </c>
     </row>
@@ -22223,7 +22250,7 @@
       <c r="V272">
         <v>248254</v>
       </c>
-      <c r="W272">
+      <c r="W272" s="1">
         <v>248254</v>
       </c>
     </row>
@@ -22294,7 +22321,7 @@
       <c r="V273">
         <v>386500</v>
       </c>
-      <c r="W273">
+      <c r="W273" s="1">
         <v>386500</v>
       </c>
     </row>
@@ -22365,7 +22392,7 @@
       <c r="V274">
         <v>7000</v>
       </c>
-      <c r="W274">
+      <c r="W274" s="1">
         <v>7000</v>
       </c>
     </row>
@@ -22436,7 +22463,7 @@
       <c r="V275">
         <v>4500</v>
       </c>
-      <c r="W275">
+      <c r="W275" s="1">
         <v>4500</v>
       </c>
     </row>
@@ -22507,7 +22534,7 @@
       <c r="V276">
         <v>-809481</v>
       </c>
-      <c r="W276">
+      <c r="W276" s="1">
         <v>595519</v>
       </c>
     </row>
@@ -22578,7 +22605,7 @@
       <c r="V277">
         <v>-2071248</v>
       </c>
-      <c r="W277">
+      <c r="W277" s="1">
         <v>36252</v>
       </c>
     </row>
@@ -22649,7 +22676,7 @@
       <c r="V278">
         <v>-5120</v>
       </c>
-      <c r="W278">
+      <c r="W278" s="1">
         <v>-5120</v>
       </c>
     </row>
@@ -22720,7 +22747,7 @@
       <c r="V279">
         <v>115528</v>
       </c>
-      <c r="W279">
+      <c r="W279" s="1">
         <v>115528</v>
       </c>
     </row>
@@ -22791,7 +22818,7 @@
       <c r="V280">
         <v>0</v>
       </c>
-      <c r="W280">
+      <c r="W280" s="1">
         <v>0</v>
       </c>
     </row>
@@ -22862,7 +22889,7 @@
       <c r="V281">
         <v>-551</v>
       </c>
-      <c r="W281">
+      <c r="W281" s="1">
         <v>-551</v>
       </c>
     </row>
@@ -22933,7 +22960,7 @@
       <c r="V282">
         <v>687750</v>
       </c>
-      <c r="W282">
+      <c r="W282" s="1">
         <v>687750</v>
       </c>
     </row>
@@ -23004,7 +23031,7 @@
       <c r="V283">
         <v>-8850</v>
       </c>
-      <c r="W283">
+      <c r="W283" s="1">
         <v>1041150</v>
       </c>
     </row>
@@ -23075,7 +23102,7 @@
       <c r="V284">
         <v>64506</v>
       </c>
-      <c r="W284">
+      <c r="W284" s="1">
         <v>64506</v>
       </c>
     </row>
@@ -23146,7 +23173,7 @@
       <c r="V285">
         <v>494500</v>
       </c>
-      <c r="W285">
+      <c r="W285" s="1">
         <v>494500</v>
       </c>
     </row>
@@ -23217,7 +23244,7 @@
       <c r="V286">
         <v>-400000</v>
       </c>
-      <c r="W286">
+      <c r="W286" s="1">
         <v>100000</v>
       </c>
     </row>
@@ -23288,7 +23315,7 @@
       <c r="V287">
         <v>30000</v>
       </c>
-      <c r="W287">
+      <c r="W287" s="1">
         <v>30000</v>
       </c>
     </row>
@@ -23359,7 +23386,7 @@
       <c r="V288">
         <v>199000</v>
       </c>
-      <c r="W288">
+      <c r="W288" s="1">
         <v>199000</v>
       </c>
     </row>
@@ -23430,7 +23457,7 @@
       <c r="V289">
         <v>0</v>
       </c>
-      <c r="W289">
+      <c r="W289" s="1">
         <v>0</v>
       </c>
     </row>
@@ -23501,7 +23528,7 @@
       <c r="V290">
         <v>899811.34</v>
       </c>
-      <c r="W290">
+      <c r="W290" s="1">
         <v>899811.34</v>
       </c>
     </row>
@@ -23572,7 +23599,7 @@
       <c r="V291">
         <v>305537.40000000002</v>
       </c>
-      <c r="W291">
+      <c r="W291" s="1">
         <v>305537.40000000002</v>
       </c>
     </row>
@@ -23643,7 +23670,7 @@
       <c r="V292">
         <v>60924.47</v>
       </c>
-      <c r="W292">
+      <c r="W292" s="1">
         <v>60924.47</v>
       </c>
     </row>
@@ -23714,7 +23741,7 @@
       <c r="V293">
         <v>26005.79</v>
       </c>
-      <c r="W293">
+      <c r="W293" s="1">
         <v>26005.79</v>
       </c>
     </row>
@@ -23785,7 +23812,7 @@
       <c r="V294">
         <v>102429.1</v>
       </c>
-      <c r="W294">
+      <c r="W294" s="1">
         <v>102429.1</v>
       </c>
     </row>
@@ -23856,7 +23883,7 @@
       <c r="V295">
         <v>144373</v>
       </c>
-      <c r="W295">
+      <c r="W295" s="1">
         <v>846873</v>
       </c>
     </row>
@@ -23927,7 +23954,7 @@
       <c r="V296">
         <v>-118766</v>
       </c>
-      <c r="W296">
+      <c r="W296" s="1">
         <v>18234</v>
       </c>
     </row>
@@ -23998,7 +24025,7 @@
       <c r="V297">
         <v>290002</v>
       </c>
-      <c r="W297">
+      <c r="W297" s="1">
         <v>290002</v>
       </c>
     </row>
@@ -24069,7 +24096,7 @@
       <c r="V298">
         <v>439645</v>
       </c>
-      <c r="W298">
+      <c r="W298" s="1">
         <v>439645</v>
       </c>
     </row>
@@ -24140,7 +24167,7 @@
       <c r="V299">
         <v>399574</v>
       </c>
-      <c r="W299">
+      <c r="W299" s="1">
         <v>399574</v>
       </c>
     </row>
@@ -24211,7 +24238,7 @@
       <c r="V300">
         <v>0</v>
       </c>
-      <c r="W300">
+      <c r="W300" s="1">
         <v>0</v>
       </c>
     </row>
@@ -24282,7 +24309,7 @@
       <c r="V301">
         <v>552600</v>
       </c>
-      <c r="W301">
+      <c r="W301" s="1">
         <v>552600</v>
       </c>
     </row>
@@ -24353,7 +24380,7 @@
       <c r="V302">
         <v>-1281</v>
       </c>
-      <c r="W302">
+      <c r="W302" s="1">
         <v>-1281</v>
       </c>
     </row>
@@ -24424,7 +24451,7 @@
       <c r="V303">
         <v>0</v>
       </c>
-      <c r="W303">
+      <c r="W303" s="1">
         <v>0</v>
       </c>
     </row>
@@ -24495,7 +24522,7 @@
       <c r="V304">
         <v>0</v>
       </c>
-      <c r="W304">
+      <c r="W304" s="1">
         <v>0</v>
       </c>
     </row>
@@ -24566,7 +24593,7 @@
       <c r="V305">
         <v>-92198</v>
       </c>
-      <c r="W305">
+      <c r="W305" s="1">
         <v>-10198</v>
       </c>
     </row>
@@ -24637,7 +24664,7 @@
       <c r="V306">
         <v>0</v>
       </c>
-      <c r="W306">
+      <c r="W306" s="1">
         <v>0</v>
       </c>
     </row>
@@ -24708,7 +24735,7 @@
       <c r="V307">
         <v>141500</v>
       </c>
-      <c r="W307">
+      <c r="W307" s="1">
         <v>141500</v>
       </c>
     </row>
@@ -24779,7 +24806,7 @@
       <c r="V308">
         <v>-500</v>
       </c>
-      <c r="W308">
+      <c r="W308" s="1">
         <v>-500</v>
       </c>
     </row>
@@ -24850,7 +24877,7 @@
       <c r="V309">
         <v>22700</v>
       </c>
-      <c r="W309">
+      <c r="W309" s="1">
         <v>22700</v>
       </c>
     </row>
@@ -24921,7 +24948,7 @@
       <c r="V310">
         <v>1506</v>
       </c>
-      <c r="W310">
+      <c r="W310" s="1">
         <v>1506</v>
       </c>
     </row>
@@ -24992,7 +25019,7 @@
       <c r="V311">
         <v>50806</v>
       </c>
-      <c r="W311">
+      <c r="W311" s="1">
         <v>50806</v>
       </c>
     </row>
@@ -25063,7 +25090,7 @@
       <c r="V312">
         <v>333398</v>
       </c>
-      <c r="W312">
+      <c r="W312" s="1">
         <v>333398</v>
       </c>
     </row>
@@ -25134,7 +25161,7 @@
       <c r="V313">
         <v>75000</v>
       </c>
-      <c r="W313">
+      <c r="W313" s="1">
         <v>75000</v>
       </c>
     </row>
@@ -25205,7 +25232,7 @@
       <c r="V314">
         <v>38100</v>
       </c>
-      <c r="W314">
+      <c r="W314" s="1">
         <v>38100</v>
       </c>
     </row>
@@ -25276,7 +25303,7 @@
       <c r="V315">
         <v>-11922.21</v>
       </c>
-      <c r="W315">
+      <c r="W315" s="1">
         <v>698077.79</v>
       </c>
     </row>
@@ -25347,7 +25374,7 @@
       <c r="V316">
         <v>293692</v>
       </c>
-      <c r="W316">
+      <c r="W316" s="1">
         <v>293692</v>
       </c>
     </row>
@@ -25418,7 +25445,7 @@
       <c r="V317">
         <v>64859</v>
       </c>
-      <c r="W317">
+      <c r="W317" s="1">
         <v>64859</v>
       </c>
     </row>
@@ -25489,7 +25516,7 @@
       <c r="V318">
         <v>-467061</v>
       </c>
-      <c r="W318">
+      <c r="W318" s="1">
         <v>32939</v>
       </c>
     </row>
@@ -25560,7 +25587,7 @@
       <c r="V319">
         <v>-1143009</v>
       </c>
-      <c r="W319">
+      <c r="W319" s="1">
         <v>56991</v>
       </c>
     </row>
@@ -25631,7 +25658,7 @@
       <c r="V320">
         <v>0</v>
       </c>
-      <c r="W320">
+      <c r="W320" s="1">
         <v>0</v>
       </c>
     </row>
@@ -25702,7 +25729,7 @@
       <c r="V321">
         <v>4050</v>
       </c>
-      <c r="W321">
+      <c r="W321" s="1">
         <v>4050</v>
       </c>
     </row>
@@ -25773,7 +25800,7 @@
       <c r="V322">
         <v>25000</v>
       </c>
-      <c r="W322">
+      <c r="W322" s="1">
         <v>25000</v>
       </c>
     </row>
@@ -25844,7 +25871,7 @@
       <c r="V323">
         <v>15</v>
       </c>
-      <c r="W323">
+      <c r="W323" s="1">
         <v>15</v>
       </c>
     </row>
@@ -25915,7 +25942,7 @@
       <c r="V324">
         <v>141340</v>
       </c>
-      <c r="W324">
+      <c r="W324" s="1">
         <v>352090</v>
       </c>
     </row>
@@ -25986,7 +26013,7 @@
       <c r="V325">
         <v>26300</v>
       </c>
-      <c r="W325">
+      <c r="W325" s="1">
         <v>26300</v>
       </c>
     </row>
@@ -26057,7 +26084,7 @@
       <c r="V326">
         <v>191500</v>
       </c>
-      <c r="W326">
+      <c r="W326" s="1">
         <v>191500</v>
       </c>
     </row>
@@ -26128,7 +26155,7 @@
       <c r="V327">
         <v>-6000</v>
       </c>
-      <c r="W327">
+      <c r="W327" s="1">
         <v>-6000</v>
       </c>
     </row>
@@ -26199,7 +26226,7 @@
       <c r="V328">
         <v>523052.42</v>
       </c>
-      <c r="W328">
+      <c r="W328" s="1">
         <v>523052.42</v>
       </c>
     </row>
@@ -26270,7 +26297,7 @@
       <c r="V329">
         <v>1037057.24</v>
       </c>
-      <c r="W329">
+      <c r="W329" s="1">
         <v>1037057.24</v>
       </c>
     </row>
@@ -26341,7 +26368,7 @@
       <c r="V330">
         <v>56039.17</v>
       </c>
-      <c r="W330">
+      <c r="W330" s="1">
         <v>56039.17</v>
       </c>
     </row>
@@ -26412,7 +26439,7 @@
       <c r="V331">
         <v>215340</v>
       </c>
-      <c r="W331">
+      <c r="W331" s="1">
         <v>215340</v>
       </c>
     </row>
@@ -26483,7 +26510,7 @@
       <c r="V332">
         <v>467465</v>
       </c>
-      <c r="W332">
+      <c r="W332" s="1">
         <v>467465</v>
       </c>
     </row>
@@ -26554,7 +26581,7 @@
       <c r="V333">
         <v>105000</v>
       </c>
-      <c r="W333">
+      <c r="W333" s="1">
         <v>105000</v>
       </c>
     </row>
@@ -26625,7 +26652,7 @@
       <c r="V334">
         <v>-1000</v>
       </c>
-      <c r="W334">
+      <c r="W334" s="1">
         <v>-1000</v>
       </c>
     </row>
@@ -26696,7 +26723,7 @@
       <c r="V335">
         <v>404217</v>
       </c>
-      <c r="W335">
+      <c r="W335" s="1">
         <v>404217</v>
       </c>
     </row>
@@ -26767,7 +26794,7 @@
       <c r="V336">
         <v>-2610</v>
       </c>
-      <c r="W336">
+      <c r="W336" s="1">
         <v>-2610</v>
       </c>
     </row>
@@ -26838,7 +26865,7 @@
       <c r="V337">
         <v>1350</v>
       </c>
-      <c r="W337">
+      <c r="W337" s="1">
         <v>1350</v>
       </c>
     </row>
@@ -26909,7 +26936,7 @@
       <c r="V338">
         <v>60000</v>
       </c>
-      <c r="W338">
+      <c r="W338" s="1">
         <v>60000</v>
       </c>
     </row>
@@ -26980,7 +27007,7 @@
       <c r="V339">
         <v>1491075</v>
       </c>
-      <c r="W339">
+      <c r="W339" s="1">
         <v>1491075</v>
       </c>
     </row>
@@ -27051,7 +27078,7 @@
       <c r="V340">
         <v>1203839.83</v>
       </c>
-      <c r="W340">
+      <c r="W340" s="1">
         <v>4203839.83</v>
       </c>
     </row>
@@ -27122,7 +27149,7 @@
       <c r="V341">
         <v>1634649.93</v>
       </c>
-      <c r="W341">
+      <c r="W341" s="1">
         <v>4634649.93</v>
       </c>
     </row>
@@ -27193,7 +27220,7 @@
       <c r="V342">
         <v>1200</v>
       </c>
-      <c r="W342">
+      <c r="W342" s="1">
         <v>1200</v>
       </c>
     </row>
@@ -27264,7 +27291,7 @@
       <c r="V343">
         <v>102525</v>
       </c>
-      <c r="W343">
+      <c r="W343" s="1">
         <v>102525</v>
       </c>
     </row>
@@ -27335,7 +27362,7 @@
       <c r="V344">
         <v>-869324.61</v>
       </c>
-      <c r="W344">
+      <c r="W344" s="1">
         <v>1014175.39</v>
       </c>
     </row>
@@ -27406,7 +27433,7 @@
       <c r="V345">
         <v>365409</v>
       </c>
-      <c r="W345">
+      <c r="W345" s="1">
         <v>2365409</v>
       </c>
     </row>
@@ -27477,7 +27504,7 @@
       <c r="V346">
         <v>-10773</v>
       </c>
-      <c r="W346">
+      <c r="W346" s="1">
         <v>-10773</v>
       </c>
     </row>
@@ -27548,7 +27575,7 @@
       <c r="V347">
         <v>-687573</v>
       </c>
-      <c r="W347">
+      <c r="W347" s="1">
         <v>1312427</v>
       </c>
     </row>
@@ -27619,7 +27646,7 @@
       <c r="V348">
         <v>-9970</v>
       </c>
-      <c r="W348">
+      <c r="W348" s="1">
         <v>-9970</v>
       </c>
     </row>
@@ -27690,7 +27717,7 @@
       <c r="V349">
         <v>68700</v>
       </c>
-      <c r="W349">
+      <c r="W349" s="1">
         <v>68700</v>
       </c>
     </row>
@@ -27761,7 +27788,7 @@
       <c r="V350">
         <v>0</v>
       </c>
-      <c r="W350">
+      <c r="W350" s="1">
         <v>0</v>
       </c>
     </row>
@@ -27832,7 +27859,7 @@
       <c r="V351">
         <v>0</v>
       </c>
-      <c r="W351">
+      <c r="W351" s="1">
         <v>0</v>
       </c>
     </row>
@@ -27903,7 +27930,7 @@
       <c r="V352">
         <v>0</v>
       </c>
-      <c r="W352">
+      <c r="W352" s="1">
         <v>0</v>
       </c>
     </row>
@@ -27974,7 +28001,7 @@
       <c r="V353">
         <v>0</v>
       </c>
-      <c r="W353">
+      <c r="W353" s="1">
         <v>0</v>
       </c>
     </row>
@@ -28045,7 +28072,7 @@
       <c r="V354">
         <v>0</v>
       </c>
-      <c r="W354">
+      <c r="W354" s="1">
         <v>0</v>
       </c>
     </row>
@@ -28116,7 +28143,7 @@
       <c r="V355">
         <v>21769</v>
       </c>
-      <c r="W355">
+      <c r="W355" s="1">
         <v>21769</v>
       </c>
     </row>
@@ -28187,7 +28214,7 @@
       <c r="V356">
         <v>-120756</v>
       </c>
-      <c r="W356">
+      <c r="W356" s="1">
         <v>-120756</v>
       </c>
     </row>
@@ -28258,7 +28285,7 @@
       <c r="V357">
         <v>1862050</v>
       </c>
-      <c r="W357">
+      <c r="W357" s="1">
         <v>2214050</v>
       </c>
     </row>
@@ -28329,7 +28356,7 @@
       <c r="V358">
         <v>-334300</v>
       </c>
-      <c r="W358">
+      <c r="W358" s="1">
         <v>165700</v>
       </c>
     </row>
@@ -28400,7 +28427,7 @@
       <c r="V359">
         <v>11800</v>
       </c>
-      <c r="W359">
+      <c r="W359" s="1">
         <v>11800</v>
       </c>
     </row>
@@ -28471,7 +28498,7 @@
       <c r="V360">
         <v>845712</v>
       </c>
-      <c r="W360">
+      <c r="W360" s="1">
         <v>845712</v>
       </c>
     </row>
@@ -28542,7 +28569,7 @@
       <c r="V361">
         <v>30000</v>
       </c>
-      <c r="W361">
+      <c r="W361" s="1">
         <v>30000</v>
       </c>
     </row>
@@ -28613,7 +28640,7 @@
       <c r="V362">
         <v>0</v>
       </c>
-      <c r="W362">
+      <c r="W362" s="1">
         <v>0</v>
       </c>
     </row>
@@ -28684,7 +28711,7 @@
       <c r="V363">
         <v>182000</v>
       </c>
-      <c r="W363">
+      <c r="W363" s="1">
         <v>182000</v>
       </c>
     </row>
@@ -28755,7 +28782,7 @@
       <c r="V364">
         <v>222072</v>
       </c>
-      <c r="W364">
+      <c r="W364" s="1">
         <v>222072</v>
       </c>
     </row>
@@ -28826,7 +28853,7 @@
       <c r="V365">
         <v>471669</v>
       </c>
-      <c r="W365">
+      <c r="W365" s="1">
         <v>471669</v>
       </c>
     </row>
@@ -28897,7 +28924,7 @@
       <c r="V366">
         <v>1195820</v>
       </c>
-      <c r="W366">
+      <c r="W366" s="1">
         <v>1195820</v>
       </c>
     </row>
@@ -28968,7 +28995,7 @@
       <c r="V367">
         <v>-592500</v>
       </c>
-      <c r="W367">
+      <c r="W367" s="1">
         <v>122500</v>
       </c>
     </row>
@@ -29039,7 +29066,7 @@
       <c r="V368">
         <v>30250</v>
       </c>
-      <c r="W368">
+      <c r="W368" s="1">
         <v>30250</v>
       </c>
     </row>
@@ -29110,7 +29137,7 @@
       <c r="V369">
         <v>175600</v>
       </c>
-      <c r="W369">
+      <c r="W369" s="1">
         <v>175600</v>
       </c>
     </row>
@@ -29181,7 +29208,7 @@
       <c r="V370">
         <v>0</v>
       </c>
-      <c r="W370">
+      <c r="W370" s="1">
         <v>0</v>
       </c>
     </row>
@@ -29252,7 +29279,7 @@
       <c r="V371">
         <v>70000</v>
       </c>
-      <c r="W371">
+      <c r="W371" s="1">
         <v>70000</v>
       </c>
     </row>
@@ -29323,7 +29350,7 @@
       <c r="V372">
         <v>0</v>
       </c>
-      <c r="W372">
+      <c r="W372" s="1">
         <v>0</v>
       </c>
     </row>
@@ -29394,7 +29421,7 @@
       <c r="V373">
         <v>0</v>
       </c>
-      <c r="W373">
+      <c r="W373" s="1">
         <v>0</v>
       </c>
     </row>
@@ -29465,7 +29492,7 @@
       <c r="V374">
         <v>0</v>
       </c>
-      <c r="W374">
+      <c r="W374" s="1">
         <v>0</v>
       </c>
     </row>
@@ -29536,7 +29563,7 @@
       <c r="V375">
         <v>-807167</v>
       </c>
-      <c r="W375">
+      <c r="W375" s="1">
         <v>-807167</v>
       </c>
     </row>
@@ -29607,7 +29634,7 @@
       <c r="V376">
         <v>0</v>
       </c>
-      <c r="W376">
+      <c r="W376" s="1">
         <v>0</v>
       </c>
     </row>
@@ -29678,7 +29705,7 @@
       <c r="V377">
         <v>-358000</v>
       </c>
-      <c r="W377">
+      <c r="W377" s="1">
         <v>-358000</v>
       </c>
     </row>
@@ -29749,7 +29776,7 @@
       <c r="V378">
         <v>-10000000</v>
       </c>
-      <c r="W378">
+      <c r="W378" s="1">
         <v>0</v>
       </c>
     </row>
@@ -29820,7 +29847,7 @@
       <c r="V379">
         <v>-15942993</v>
       </c>
-      <c r="W379">
+      <c r="W379" s="1">
         <v>-5942993</v>
       </c>
     </row>
@@ -29891,7 +29918,7 @@
       <c r="V380">
         <v>-10007100</v>
       </c>
-      <c r="W380">
+      <c r="W380" s="1">
         <v>-7100</v>
       </c>
     </row>
@@ -29962,7 +29989,7 @@
       <c r="V381">
         <v>-368000</v>
       </c>
-      <c r="W381">
+      <c r="W381" s="1">
         <v>1132000</v>
       </c>
     </row>
@@ -30033,7 +30060,7 @@
       <c r="V382">
         <v>-1319800</v>
       </c>
-      <c r="W382">
+      <c r="W382" s="1">
         <v>180200</v>
       </c>
     </row>
@@ -30104,7 +30131,7 @@
       <c r="V383">
         <v>-3081540</v>
       </c>
-      <c r="W383">
+      <c r="W383" s="1">
         <v>-3081540</v>
       </c>
     </row>
@@ -30175,7 +30202,7 @@
       <c r="V384">
         <v>-18575422</v>
       </c>
-      <c r="W384">
+      <c r="W384" s="1">
         <v>-18575422</v>
       </c>
     </row>
@@ -30246,7 +30273,7 @@
       <c r="V385">
         <v>-999150</v>
       </c>
-      <c r="W385">
+      <c r="W385" s="1">
         <v>-999150</v>
       </c>
     </row>
@@ -30317,7 +30344,7 @@
       <c r="V386">
         <v>0</v>
       </c>
-      <c r="W386">
+      <c r="W386" s="1">
         <v>0</v>
       </c>
     </row>
@@ -30388,7 +30415,7 @@
       <c r="V387">
         <v>0</v>
       </c>
-      <c r="W387">
+      <c r="W387" s="1">
         <v>0</v>
       </c>
     </row>
@@ -30459,7 +30486,7 @@
       <c r="V388">
         <v>0</v>
       </c>
-      <c r="W388">
+      <c r="W388" s="1">
         <v>0</v>
       </c>
     </row>
@@ -30530,7 +30557,7 @@
       <c r="V389">
         <v>0</v>
       </c>
-      <c r="W389">
+      <c r="W389" s="1">
         <v>0</v>
       </c>
     </row>
@@ -30601,7 +30628,7 @@
       <c r="V390">
         <v>61995</v>
       </c>
-      <c r="W390">
+      <c r="W390" s="1">
         <v>61995</v>
       </c>
     </row>
@@ -30672,7 +30699,7 @@
       <c r="V391">
         <v>0</v>
       </c>
-      <c r="W391">
+      <c r="W391" s="1">
         <v>0</v>
       </c>
     </row>
@@ -30743,7 +30770,7 @@
       <c r="V392">
         <v>-420000</v>
       </c>
-      <c r="W392">
+      <c r="W392" s="1">
         <v>-420000</v>
       </c>
     </row>
@@ -30814,7 +30841,7 @@
       <c r="V393">
         <v>0</v>
       </c>
-      <c r="W393">
+      <c r="W393" s="1">
         <v>0</v>
       </c>
     </row>
@@ -30885,7 +30912,7 @@
       <c r="V394">
         <v>0</v>
       </c>
-      <c r="W394">
+      <c r="W394" s="1">
         <v>0</v>
       </c>
     </row>
@@ -30956,7 +30983,7 @@
       <c r="V395">
         <v>0</v>
       </c>
-      <c r="W395">
+      <c r="W395" s="1">
         <v>0</v>
       </c>
     </row>
@@ -31027,7 +31054,7 @@
       <c r="V396">
         <v>-1045816</v>
       </c>
-      <c r="W396">
+      <c r="W396" s="1">
         <v>-1045816</v>
       </c>
     </row>
@@ -31098,7 +31125,7 @@
       <c r="V397">
         <v>-24980</v>
       </c>
-      <c r="W397">
+      <c r="W397" s="1">
         <v>-24980</v>
       </c>
     </row>
@@ -31169,7 +31196,7 @@
       <c r="V398">
         <v>-584969</v>
       </c>
-      <c r="W398">
+      <c r="W398" s="1">
         <v>-584969</v>
       </c>
     </row>
@@ -31240,7 +31267,7 @@
       <c r="V399">
         <v>0</v>
       </c>
-      <c r="W399">
+      <c r="W399" s="1">
         <v>0</v>
       </c>
     </row>
@@ -31311,7 +31338,7 @@
       <c r="V400">
         <v>0</v>
       </c>
-      <c r="W400">
+      <c r="W400" s="1">
         <v>0</v>
       </c>
     </row>
@@ -31382,7 +31409,7 @@
       <c r="V401">
         <v>0</v>
       </c>
-      <c r="W401">
+      <c r="W401" s="1">
         <v>0</v>
       </c>
     </row>
@@ -31453,7 +31480,7 @@
       <c r="V402">
         <v>-31000</v>
       </c>
-      <c r="W402">
+      <c r="W402" s="1">
         <v>-31000</v>
       </c>
     </row>
@@ -31524,7 +31551,7 @@
       <c r="V403">
         <v>0</v>
       </c>
-      <c r="W403">
+      <c r="W403" s="1">
         <v>0</v>
       </c>
     </row>
@@ -31595,7 +31622,7 @@
       <c r="V404">
         <v>0</v>
       </c>
-      <c r="W404">
+      <c r="W404" s="1">
         <v>0</v>
       </c>
     </row>
@@ -31666,7 +31693,7 @@
       <c r="V405">
         <v>-2695200</v>
       </c>
-      <c r="W405">
+      <c r="W405" s="1">
         <v>-2695200</v>
       </c>
     </row>
@@ -31737,7 +31764,7 @@
       <c r="V406">
         <v>-6812131</v>
       </c>
-      <c r="W406">
+      <c r="W406" s="1">
         <v>-6812131</v>
       </c>
     </row>
@@ -31808,7 +31835,7 @@
       <c r="V407">
         <v>75940</v>
       </c>
-      <c r="W407">
+      <c r="W407" s="1">
         <v>75940</v>
       </c>
     </row>
@@ -31879,7 +31906,7 @@
       <c r="V408">
         <v>0</v>
       </c>
-      <c r="W408">
+      <c r="W408" s="1">
         <v>0</v>
       </c>
     </row>
@@ -31950,7 +31977,7 @@
       <c r="V409">
         <v>0</v>
       </c>
-      <c r="W409">
+      <c r="W409" s="1">
         <v>0</v>
       </c>
     </row>
@@ -32021,7 +32048,7 @@
       <c r="V410">
         <v>0</v>
       </c>
-      <c r="W410">
+      <c r="W410" s="1">
         <v>0</v>
       </c>
     </row>
@@ -32092,7 +32119,7 @@
       <c r="V411">
         <v>0</v>
       </c>
-      <c r="W411">
+      <c r="W411" s="1">
         <v>0</v>
       </c>
     </row>
@@ -32163,7 +32190,7 @@
       <c r="V412">
         <v>-549800</v>
       </c>
-      <c r="W412">
+      <c r="W412" s="1">
         <v>-549800</v>
       </c>
     </row>
@@ -32234,7 +32261,7 @@
       <c r="V413">
         <v>0</v>
       </c>
-      <c r="W413">
+      <c r="W413" s="1">
         <v>0</v>
       </c>
     </row>
@@ -32305,7 +32332,7 @@
       <c r="V414">
         <v>0</v>
       </c>
-      <c r="W414">
+      <c r="W414" s="1">
         <v>0</v>
       </c>
     </row>
@@ -32376,7 +32403,7 @@
       <c r="V415">
         <v>-3046400</v>
       </c>
-      <c r="W415">
+      <c r="W415" s="1">
         <v>-3046400</v>
       </c>
     </row>
@@ -32447,7 +32474,7 @@
       <c r="V416">
         <v>-114751</v>
       </c>
-      <c r="W416">
+      <c r="W416" s="1">
         <v>-114751</v>
       </c>
     </row>
@@ -32518,7 +32545,7 @@
       <c r="V417">
         <v>-588983</v>
       </c>
-      <c r="W417">
+      <c r="W417" s="1">
         <v>-588983</v>
       </c>
     </row>
@@ -32589,7 +32616,7 @@
       <c r="V418">
         <v>-432975</v>
       </c>
-      <c r="W418">
+      <c r="W418" s="1">
         <v>-432975</v>
       </c>
     </row>
@@ -32660,7 +32687,7 @@
       <c r="V419">
         <v>-89910</v>
       </c>
-      <c r="W419">
+      <c r="W419" s="1">
         <v>-89910</v>
       </c>
     </row>
@@ -32731,7 +32758,7 @@
       <c r="V420">
         <v>-332150</v>
       </c>
-      <c r="W420">
+      <c r="W420" s="1">
         <v>-332150</v>
       </c>
     </row>
@@ -32802,7 +32829,7 @@
       <c r="V421">
         <v>-130420</v>
       </c>
-      <c r="W421">
+      <c r="W421" s="1">
         <v>-130420</v>
       </c>
     </row>
@@ -32873,7 +32900,7 @@
       <c r="V422">
         <v>0</v>
       </c>
-      <c r="W422">
+      <c r="W422" s="1">
         <v>0</v>
       </c>
     </row>
@@ -32944,7 +32971,7 @@
       <c r="V423">
         <v>162713606</v>
       </c>
-      <c r="W423">
+      <c r="W423" s="1">
         <v>162713606</v>
       </c>
     </row>
@@ -33015,7 +33042,7 @@
       <c r="V424">
         <v>21601392</v>
       </c>
-      <c r="W424">
+      <c r="W424" s="1">
         <v>21601392</v>
       </c>
     </row>
@@ -33086,7 +33113,7 @@
       <c r="V425">
         <v>-80034551</v>
       </c>
-      <c r="W425">
+      <c r="W425" s="1">
         <v>19965449</v>
       </c>
     </row>
@@ -33157,7 +33184,7 @@
       <c r="V426">
         <v>210335</v>
       </c>
-      <c r="W426">
+      <c r="W426" s="1">
         <v>210335</v>
       </c>
     </row>
@@ -33228,7 +33255,7 @@
       <c r="V427">
         <v>102024058</v>
       </c>
-      <c r="W427">
+      <c r="W427" s="1">
         <v>102024058</v>
       </c>
     </row>
@@ -33299,7 +33326,7 @@
       <c r="V428">
         <v>-1323695</v>
       </c>
-      <c r="W428">
+      <c r="W428" s="1">
         <v>-1323695</v>
       </c>
     </row>
@@ -33370,7 +33397,7 @@
       <c r="V429">
         <v>18636427</v>
       </c>
-      <c r="W429">
+      <c r="W429" s="1">
         <v>18636427</v>
       </c>
     </row>
@@ -33441,7 +33468,7 @@
       <c r="V430">
         <v>-1200527</v>
       </c>
-      <c r="W430">
+      <c r="W430" s="1">
         <v>-1200527</v>
       </c>
     </row>
@@ -33512,7 +33539,7 @@
       <c r="V431">
         <v>-25469702</v>
       </c>
-      <c r="W431">
+      <c r="W431" s="1">
         <v>-25469702</v>
       </c>
     </row>
@@ -33583,7 +33610,7 @@
       <c r="V432">
         <v>-530000</v>
       </c>
-      <c r="W432">
+      <c r="W432" s="1">
         <v>-530000</v>
       </c>
     </row>
@@ -33654,7 +33681,7 @@
       <c r="V433">
         <v>44957287</v>
       </c>
-      <c r="W433">
+      <c r="W433" s="1">
         <v>44957287</v>
       </c>
     </row>
@@ -33725,7 +33752,7 @@
       <c r="V434">
         <v>-81370193</v>
       </c>
-      <c r="W434">
+      <c r="W434" s="1">
         <v>18629807</v>
       </c>
     </row>
@@ -33796,7 +33823,7 @@
       <c r="V435">
         <v>4219524</v>
       </c>
-      <c r="W435">
+      <c r="W435" s="1">
         <v>4219524</v>
       </c>
     </row>
@@ -33867,7 +33894,7 @@
       <c r="V436">
         <v>1010000</v>
       </c>
-      <c r="W436">
+      <c r="W436" s="1">
         <v>1010000</v>
       </c>
     </row>
@@ -33938,7 +33965,7 @@
       <c r="V437">
         <v>0.21</v>
       </c>
-      <c r="W437">
+      <c r="W437" s="1">
         <v>0.21</v>
       </c>
     </row>
@@ -34009,7 +34036,7 @@
       <c r="V438">
         <v>-0.16</v>
       </c>
-      <c r="W438">
+      <c r="W438" s="1">
         <v>-0.16</v>
       </c>
     </row>
@@ -34080,7 +34107,7 @@
       <c r="V439">
         <v>1882</v>
       </c>
-      <c r="W439">
+      <c r="W439" s="1">
         <v>1882</v>
       </c>
     </row>
@@ -34151,7 +34178,7 @@
       <c r="V440">
         <v>0</v>
       </c>
-      <c r="W440">
+      <c r="W440" s="1">
         <v>0</v>
       </c>
     </row>
@@ -34222,7 +34249,7 @@
       <c r="V441">
         <v>0</v>
       </c>
-      <c r="W441">
+      <c r="W441" s="1">
         <v>0</v>
       </c>
     </row>
@@ -34293,7 +34320,7 @@
       <c r="V442">
         <v>0</v>
       </c>
-      <c r="W442">
+      <c r="W442" s="1">
         <v>0</v>
       </c>
     </row>
@@ -34364,7 +34391,7 @@
       <c r="V443">
         <v>0.09</v>
       </c>
-      <c r="W443">
+      <c r="W443" s="1">
         <v>0.09</v>
       </c>
     </row>
@@ -34435,7 +34462,7 @@
       <c r="V444">
         <v>0</v>
       </c>
-      <c r="W444">
+      <c r="W444" s="1">
         <v>0</v>
       </c>
     </row>
@@ -34506,7 +34533,7 @@
       <c r="V445">
         <v>0</v>
       </c>
-      <c r="W445">
+      <c r="W445" s="1">
         <v>0</v>
       </c>
     </row>
@@ -34577,7 +34604,7 @@
       <c r="V446">
         <v>4387.12</v>
       </c>
-      <c r="W446">
+      <c r="W446" s="1">
         <v>4387.12</v>
       </c>
     </row>
@@ -34648,7 +34675,7 @@
       <c r="V447">
         <v>7800</v>
       </c>
-      <c r="W447">
+      <c r="W447" s="1">
         <v>7800</v>
       </c>
     </row>
@@ -34719,7 +34746,7 @@
       <c r="V448">
         <v>11676.8</v>
       </c>
-      <c r="W448">
+      <c r="W448" s="1">
         <v>11676.8</v>
       </c>
     </row>
@@ -34790,7 +34817,7 @@
       <c r="V449">
         <v>46251</v>
       </c>
-      <c r="W449">
+      <c r="W449" s="1">
         <v>46251</v>
       </c>
     </row>
@@ -34861,7 +34888,7 @@
       <c r="V450">
         <v>85100</v>
       </c>
-      <c r="W450">
+      <c r="W450" s="1">
         <v>85100</v>
       </c>
     </row>
@@ -34932,7 +34959,7 @@
       <c r="V451">
         <v>0</v>
       </c>
-      <c r="W451">
+      <c r="W451" s="1">
         <v>0</v>
       </c>
     </row>
@@ -35003,7 +35030,7 @@
       <c r="V452">
         <v>0</v>
       </c>
-      <c r="W452">
+      <c r="W452" s="1">
         <v>0</v>
       </c>
     </row>
@@ -35074,7 +35101,7 @@
       <c r="V453">
         <v>0</v>
       </c>
-      <c r="W453">
+      <c r="W453" s="1">
         <v>0</v>
       </c>
     </row>
@@ -35145,7 +35172,7 @@
       <c r="V454">
         <v>-44739</v>
       </c>
-      <c r="W454">
+      <c r="W454" s="1">
         <v>-44739</v>
       </c>
     </row>
@@ -35216,7 +35243,7 @@
       <c r="V455">
         <v>78773</v>
       </c>
-      <c r="W455">
+      <c r="W455" s="1">
         <v>78773</v>
       </c>
     </row>
@@ -35287,7 +35314,7 @@
       <c r="V456">
         <v>0</v>
       </c>
-      <c r="W456">
+      <c r="W456" s="1">
         <v>0</v>
       </c>
     </row>
@@ -35358,7 +35385,7 @@
       <c r="V457">
         <v>4014.78</v>
       </c>
-      <c r="W457">
+      <c r="W457" s="1">
         <v>4014.78</v>
       </c>
     </row>
@@ -35429,7 +35456,7 @@
       <c r="V458">
         <v>0</v>
       </c>
-      <c r="W458">
+      <c r="W458" s="1">
         <v>0</v>
       </c>
     </row>
@@ -35500,7 +35527,7 @@
       <c r="V459">
         <v>0</v>
       </c>
-      <c r="W459">
+      <c r="W459" s="1">
         <v>0</v>
       </c>
     </row>
@@ -35571,7 +35598,7 @@
       <c r="V460">
         <v>0</v>
       </c>
-      <c r="W460">
+      <c r="W460" s="1">
         <v>0</v>
       </c>
     </row>
@@ -35642,7 +35669,7 @@
       <c r="V461">
         <v>0</v>
       </c>
-      <c r="W461">
+      <c r="W461" s="1">
         <v>0</v>
       </c>
     </row>
@@ -35713,7 +35740,7 @@
       <c r="V462">
         <v>10000</v>
       </c>
-      <c r="W462">
+      <c r="W462" s="1">
         <v>10000</v>
       </c>
     </row>
@@ -35784,7 +35811,7 @@
       <c r="V463">
         <v>4960</v>
       </c>
-      <c r="W463">
+      <c r="W463" s="1">
         <v>4960</v>
       </c>
     </row>
@@ -35855,7 +35882,7 @@
       <c r="V464">
         <v>0</v>
       </c>
-      <c r="W464">
+      <c r="W464" s="1">
         <v>0</v>
       </c>
     </row>
@@ -35926,7 +35953,7 @@
       <c r="V465">
         <v>0</v>
       </c>
-      <c r="W465">
+      <c r="W465" s="1">
         <v>0</v>
       </c>
     </row>
@@ -35997,7 +36024,7 @@
       <c r="V466">
         <v>96</v>
       </c>
-      <c r="W466">
+      <c r="W466" s="1">
         <v>96</v>
       </c>
     </row>
@@ -36068,7 +36095,7 @@
       <c r="V467">
         <v>4200</v>
       </c>
-      <c r="W467">
+      <c r="W467" s="1">
         <v>4200</v>
       </c>
     </row>
@@ -36139,7 +36166,7 @@
       <c r="V468">
         <v>14.4</v>
       </c>
-      <c r="W468">
+      <c r="W468" s="1">
         <v>14.4</v>
       </c>
     </row>
@@ -36210,7 +36237,7 @@
       <c r="V469">
         <v>12360</v>
       </c>
-      <c r="W469">
+      <c r="W469" s="1">
         <v>12360</v>
       </c>
     </row>
@@ -36281,7 +36308,7 @@
       <c r="V470">
         <v>645301.37</v>
       </c>
-      <c r="W470">
+      <c r="W470" s="1">
         <v>645301.37</v>
       </c>
     </row>
@@ -36352,7 +36379,7 @@
       <c r="V471">
         <v>0</v>
       </c>
-      <c r="W471">
+      <c r="W471" s="1">
         <v>0</v>
       </c>
     </row>
@@ -36423,7 +36450,7 @@
       <c r="V472">
         <v>0</v>
       </c>
-      <c r="W472">
+      <c r="W472" s="1">
         <v>0</v>
       </c>
     </row>
@@ -36494,7 +36521,7 @@
       <c r="V473">
         <v>0</v>
       </c>
-      <c r="W473">
+      <c r="W473" s="1">
         <v>0</v>
       </c>
     </row>
@@ -36565,7 +36592,7 @@
       <c r="V474">
         <v>0</v>
       </c>
-      <c r="W474">
+      <c r="W474" s="1">
         <v>0</v>
       </c>
     </row>
@@ -36636,7 +36663,7 @@
       <c r="V475">
         <v>0</v>
       </c>
-      <c r="W475">
+      <c r="W475" s="1">
         <v>0</v>
       </c>
     </row>
@@ -36707,7 +36734,7 @@
       <c r="V476">
         <v>0</v>
       </c>
-      <c r="W476">
+      <c r="W476" s="1">
         <v>0</v>
       </c>
     </row>
@@ -36778,7 +36805,7 @@
       <c r="V477">
         <v>0</v>
       </c>
-      <c r="W477">
+      <c r="W477" s="1">
         <v>0</v>
       </c>
     </row>
@@ -36849,7 +36876,7 @@
       <c r="V478">
         <v>0</v>
       </c>
-      <c r="W478">
+      <c r="W478" s="1">
         <v>0</v>
       </c>
     </row>
@@ -36920,7 +36947,7 @@
       <c r="V479">
         <v>66500</v>
       </c>
-      <c r="W479">
+      <c r="W479" s="1">
         <v>66500</v>
       </c>
     </row>
@@ -36991,7 +37018,7 @@
       <c r="V480">
         <v>0</v>
       </c>
-      <c r="W480">
+      <c r="W480" s="1">
         <v>0</v>
       </c>
     </row>
@@ -37062,7 +37089,7 @@
       <c r="V481">
         <v>0</v>
       </c>
-      <c r="W481">
+      <c r="W481" s="1">
         <v>0</v>
       </c>
     </row>
@@ -37133,7 +37160,7 @@
       <c r="V482">
         <v>0</v>
       </c>
-      <c r="W482">
+      <c r="W482" s="1">
         <v>0</v>
       </c>
     </row>
@@ -37204,7 +37231,7 @@
       <c r="V483">
         <v>0</v>
       </c>
-      <c r="W483">
+      <c r="W483" s="1">
         <v>0</v>
       </c>
     </row>
@@ -37275,7 +37302,7 @@
       <c r="V484">
         <v>0</v>
       </c>
-      <c r="W484">
+      <c r="W484" s="1">
         <v>0</v>
       </c>
     </row>
@@ -37346,7 +37373,7 @@
       <c r="V485">
         <v>0</v>
       </c>
-      <c r="W485">
+      <c r="W485" s="1">
         <v>0</v>
       </c>
     </row>
@@ -37417,7 +37444,7 @@
       <c r="V486">
         <v>0</v>
       </c>
-      <c r="W486">
+      <c r="W486" s="1">
         <v>0</v>
       </c>
     </row>
@@ -37488,7 +37515,7 @@
       <c r="V487">
         <v>0</v>
       </c>
-      <c r="W487">
+      <c r="W487" s="1">
         <v>0</v>
       </c>
     </row>
@@ -37559,7 +37586,7 @@
       <c r="V488">
         <v>0</v>
       </c>
-      <c r="W488">
+      <c r="W488" s="1">
         <v>0</v>
       </c>
     </row>
@@ -37630,7 +37657,7 @@
       <c r="V489">
         <v>0</v>
       </c>
-      <c r="W489">
+      <c r="W489" s="1">
         <v>0</v>
       </c>
     </row>
@@ -37701,7 +37728,7 @@
       <c r="V490">
         <v>0</v>
       </c>
-      <c r="W490">
+      <c r="W490" s="1">
         <v>0</v>
       </c>
     </row>
@@ -37772,7 +37799,7 @@
       <c r="V491">
         <v>0</v>
       </c>
-      <c r="W491">
+      <c r="W491" s="1">
         <v>0</v>
       </c>
     </row>
@@ -37843,7 +37870,7 @@
       <c r="V492">
         <v>0</v>
       </c>
-      <c r="W492">
+      <c r="W492" s="1">
         <v>0</v>
       </c>
     </row>
@@ -37914,7 +37941,7 @@
       <c r="V493">
         <v>0</v>
       </c>
-      <c r="W493">
+      <c r="W493" s="1">
         <v>0</v>
       </c>
     </row>
@@ -37985,7 +38012,7 @@
       <c r="V494">
         <v>0</v>
       </c>
-      <c r="W494">
+      <c r="W494" s="1">
         <v>0</v>
       </c>
     </row>
@@ -38056,7 +38083,7 @@
       <c r="V495">
         <v>0</v>
       </c>
-      <c r="W495">
+      <c r="W495" s="1">
         <v>0</v>
       </c>
     </row>
@@ -38127,7 +38154,7 @@
       <c r="V496">
         <v>0</v>
       </c>
-      <c r="W496">
+      <c r="W496" s="1">
         <v>0</v>
       </c>
     </row>
@@ -38198,7 +38225,7 @@
       <c r="V497">
         <v>31650</v>
       </c>
-      <c r="W497">
+      <c r="W497" s="1">
         <v>31650</v>
       </c>
     </row>
@@ -38269,7 +38296,7 @@
       <c r="V498">
         <v>123848</v>
       </c>
-      <c r="W498">
+      <c r="W498" s="1">
         <v>123848</v>
       </c>
     </row>
@@ -38340,7 +38367,7 @@
       <c r="V499">
         <v>0</v>
       </c>
-      <c r="W499">
+      <c r="W499" s="1">
         <v>0</v>
       </c>
     </row>
@@ -38411,7 +38438,7 @@
       <c r="V500">
         <v>-200</v>
       </c>
-      <c r="W500">
+      <c r="W500" s="1">
         <v>-200</v>
       </c>
     </row>
@@ -38482,7 +38509,7 @@
       <c r="V501">
         <v>740</v>
       </c>
-      <c r="W501">
+      <c r="W501" s="1">
         <v>740</v>
       </c>
     </row>
@@ -38553,7 +38580,7 @@
       <c r="V502">
         <v>50</v>
       </c>
-      <c r="W502">
+      <c r="W502" s="1">
         <v>50</v>
       </c>
     </row>
@@ -38624,7 +38651,7 @@
       <c r="V503">
         <v>468756</v>
       </c>
-      <c r="W503">
+      <c r="W503" s="1">
         <v>468756</v>
       </c>
     </row>
@@ -38695,7 +38722,7 @@
       <c r="V504">
         <v>0</v>
       </c>
-      <c r="W504">
+      <c r="W504" s="1">
         <v>0</v>
       </c>
     </row>
@@ -38766,7 +38793,7 @@
       <c r="V505">
         <v>0</v>
       </c>
-      <c r="W505">
+      <c r="W505" s="1">
         <v>0</v>
       </c>
     </row>
@@ -38837,7 +38864,7 @@
       <c r="V506">
         <v>0</v>
       </c>
-      <c r="W506">
+      <c r="W506" s="1">
         <v>0</v>
       </c>
     </row>
@@ -38908,7 +38935,7 @@
       <c r="V507">
         <v>0</v>
       </c>
-      <c r="W507">
+      <c r="W507" s="1">
         <v>0</v>
       </c>
     </row>
@@ -38979,7 +39006,7 @@
       <c r="V508">
         <v>0</v>
       </c>
-      <c r="W508">
+      <c r="W508" s="1">
         <v>0</v>
       </c>
     </row>
@@ -39050,7 +39077,7 @@
       <c r="V509">
         <v>200</v>
       </c>
-      <c r="W509">
+      <c r="W509" s="1">
         <v>200</v>
       </c>
     </row>
@@ -39121,7 +39148,7 @@
       <c r="V510">
         <v>0</v>
       </c>
-      <c r="W510">
+      <c r="W510" s="1">
         <v>0</v>
       </c>
     </row>
@@ -39192,7 +39219,7 @@
       <c r="V511">
         <v>0</v>
       </c>
-      <c r="W511">
+      <c r="W511" s="1">
         <v>0</v>
       </c>
     </row>
@@ -39263,7 +39290,7 @@
       <c r="V512">
         <v>0</v>
       </c>
-      <c r="W512">
+      <c r="W512" s="1">
         <v>0</v>
       </c>
     </row>
@@ -39334,7 +39361,7 @@
       <c r="V513">
         <v>1240</v>
       </c>
-      <c r="W513">
+      <c r="W513" s="1">
         <v>1240</v>
       </c>
     </row>
@@ -39405,7 +39432,7 @@
       <c r="V514">
         <v>0</v>
       </c>
-      <c r="W514">
+      <c r="W514" s="1">
         <v>0</v>
       </c>
     </row>
@@ -39476,7 +39503,7 @@
       <c r="V515">
         <v>0</v>
       </c>
-      <c r="W515">
+      <c r="W515" s="1">
         <v>0</v>
       </c>
     </row>
@@ -39547,7 +39574,7 @@
       <c r="V516">
         <v>0</v>
       </c>
-      <c r="W516">
+      <c r="W516" s="1">
         <v>0</v>
       </c>
     </row>
@@ -39618,7 +39645,7 @@
       <c r="V517">
         <v>0</v>
       </c>
-      <c r="W517">
+      <c r="W517" s="1">
         <v>0</v>
       </c>
     </row>
@@ -39689,7 +39716,7 @@
       <c r="V518">
         <v>3250</v>
       </c>
-      <c r="W518">
+      <c r="W518" s="1">
         <v>3250</v>
       </c>
     </row>
@@ -39760,7 +39787,7 @@
       <c r="V519">
         <v>324342</v>
       </c>
-      <c r="W519">
+      <c r="W519" s="1">
         <v>324342</v>
       </c>
     </row>
@@ -39831,7 +39858,7 @@
       <c r="V520">
         <v>7456</v>
       </c>
-      <c r="W520">
+      <c r="W520" s="1">
         <v>7456</v>
       </c>
     </row>
@@ -39902,7 +39929,7 @@
       <c r="V521">
         <v>0</v>
       </c>
-      <c r="W521">
+      <c r="W521" s="1">
         <v>0</v>
       </c>
     </row>
@@ -39973,7 +40000,7 @@
       <c r="V522">
         <v>0</v>
       </c>
-      <c r="W522">
+      <c r="W522" s="1">
         <v>0</v>
       </c>
     </row>
@@ -40044,7 +40071,7 @@
       <c r="V523">
         <v>0</v>
       </c>
-      <c r="W523">
+      <c r="W523" s="1">
         <v>0</v>
       </c>
     </row>
@@ -40115,7 +40142,7 @@
       <c r="V524">
         <v>6</v>
       </c>
-      <c r="W524">
+      <c r="W524" s="1">
         <v>6</v>
       </c>
     </row>
@@ -40186,7 +40213,7 @@
       <c r="V525">
         <v>0</v>
       </c>
-      <c r="W525">
+      <c r="W525" s="1">
         <v>0</v>
       </c>
     </row>
@@ -40257,7 +40284,7 @@
       <c r="V526">
         <v>500</v>
       </c>
-      <c r="W526">
+      <c r="W526" s="1">
         <v>500</v>
       </c>
     </row>
@@ -40328,7 +40355,7 @@
       <c r="V527">
         <v>45316</v>
       </c>
-      <c r="W527">
+      <c r="W527" s="1">
         <v>45316</v>
       </c>
     </row>
@@ -40399,7 +40426,7 @@
       <c r="V528">
         <v>0</v>
       </c>
-      <c r="W528">
+      <c r="W528" s="1">
         <v>0</v>
       </c>
     </row>
@@ -40470,7 +40497,7 @@
       <c r="V529">
         <v>-11064</v>
       </c>
-      <c r="W529">
+      <c r="W529" s="1">
         <v>-11064</v>
       </c>
     </row>
@@ -40541,7 +40568,7 @@
       <c r="V530">
         <v>0</v>
       </c>
-      <c r="W530">
+      <c r="W530" s="1">
         <v>0</v>
       </c>
     </row>
@@ -40612,7 +40639,7 @@
       <c r="V531">
         <v>0</v>
       </c>
-      <c r="W531">
+      <c r="W531" s="1">
         <v>0</v>
       </c>
     </row>
@@ -40683,7 +40710,7 @@
       <c r="V532">
         <v>69664</v>
       </c>
-      <c r="W532">
+      <c r="W532" s="1">
         <v>69664</v>
       </c>
     </row>
@@ -40754,7 +40781,7 @@
       <c r="V533">
         <v>-22182</v>
       </c>
-      <c r="W533">
+      <c r="W533" s="1">
         <v>-22182</v>
       </c>
     </row>
@@ -40825,7 +40852,7 @@
       <c r="V534">
         <v>0</v>
       </c>
-      <c r="W534">
+      <c r="W534" s="1">
         <v>0</v>
       </c>
     </row>
@@ -40896,7 +40923,7 @@
       <c r="V535">
         <v>0</v>
       </c>
-      <c r="W535">
+      <c r="W535" s="1">
         <v>0</v>
       </c>
     </row>
@@ -40967,7 +40994,7 @@
       <c r="V536">
         <v>0</v>
       </c>
-      <c r="W536">
+      <c r="W536" s="1">
         <v>0</v>
       </c>
     </row>
@@ -41038,7 +41065,7 @@
       <c r="V537">
         <v>28762</v>
       </c>
-      <c r="W537">
+      <c r="W537" s="1">
         <v>28762</v>
       </c>
     </row>
@@ -41109,7 +41136,7 @@
       <c r="V538">
         <v>0</v>
       </c>
-      <c r="W538">
+      <c r="W538" s="1">
         <v>0</v>
       </c>
     </row>
@@ -41180,7 +41207,7 @@
       <c r="V539">
         <v>50209</v>
       </c>
-      <c r="W539">
+      <c r="W539" s="1">
         <v>50209</v>
       </c>
     </row>
@@ -41251,7 +41278,7 @@
       <c r="V540">
         <v>43500</v>
       </c>
-      <c r="W540">
+      <c r="W540" s="1">
         <v>43500</v>
       </c>
     </row>
@@ -41322,7 +41349,7 @@
       <c r="V541">
         <v>0</v>
       </c>
-      <c r="W541">
+      <c r="W541" s="1">
         <v>0</v>
       </c>
     </row>
@@ -41393,7 +41420,7 @@
       <c r="V542">
         <v>-240800</v>
       </c>
-      <c r="W542">
+      <c r="W542" s="1">
         <v>40200</v>
       </c>
     </row>
@@ -41464,7 +41491,7 @@
       <c r="V543">
         <v>0</v>
       </c>
-      <c r="W543">
+      <c r="W543" s="1">
         <v>0</v>
       </c>
     </row>
@@ -41535,7 +41562,7 @@
       <c r="V544">
         <v>150552</v>
       </c>
-      <c r="W544">
+      <c r="W544" s="1">
         <v>150552</v>
       </c>
     </row>
@@ -41606,7 +41633,7 @@
       <c r="V545">
         <v>800</v>
       </c>
-      <c r="W545">
+      <c r="W545" s="1">
         <v>800</v>
       </c>
     </row>
@@ -41677,7 +41704,7 @@
       <c r="V546">
         <v>-18368</v>
       </c>
-      <c r="W546">
+      <c r="W546" s="1">
         <v>-18368</v>
       </c>
     </row>
@@ -41748,7 +41775,7 @@
       <c r="V547">
         <v>18300</v>
       </c>
-      <c r="W547">
+      <c r="W547" s="1">
         <v>18300</v>
       </c>
     </row>
@@ -41819,7 +41846,7 @@
       <c r="V548">
         <v>0</v>
       </c>
-      <c r="W548">
+      <c r="W548" s="1">
         <v>0</v>
       </c>
     </row>
@@ -41890,7 +41917,7 @@
       <c r="V549">
         <v>44350</v>
       </c>
-      <c r="W549">
+      <c r="W549" s="1">
         <v>44350</v>
       </c>
     </row>
@@ -41961,7 +41988,7 @@
       <c r="V550">
         <v>0</v>
       </c>
-      <c r="W550">
+      <c r="W550" s="1">
         <v>0</v>
       </c>
     </row>
@@ -42032,7 +42059,7 @@
       <c r="V551">
         <v>40800</v>
       </c>
-      <c r="W551">
+      <c r="W551" s="1">
         <v>40800</v>
       </c>
     </row>
@@ -42103,7 +42130,7 @@
       <c r="V552">
         <v>13408</v>
       </c>
-      <c r="W552">
+      <c r="W552" s="1">
         <v>13408</v>
       </c>
     </row>
@@ -42174,7 +42201,7 @@
       <c r="V553">
         <v>-39310</v>
       </c>
-      <c r="W553">
+      <c r="W553" s="1">
         <v>-39310</v>
       </c>
     </row>
@@ -42245,7 +42272,7 @@
       <c r="V554">
         <v>0</v>
       </c>
-      <c r="W554">
+      <c r="W554" s="1">
         <v>0</v>
       </c>
     </row>
@@ -42316,7 +42343,7 @@
       <c r="V555">
         <v>25000</v>
       </c>
-      <c r="W555">
+      <c r="W555" s="1">
         <v>25000</v>
       </c>
     </row>
@@ -42387,7 +42414,7 @@
       <c r="V556">
         <v>23680</v>
       </c>
-      <c r="W556">
+      <c r="W556" s="1">
         <v>23680</v>
       </c>
     </row>
@@ -42458,7 +42485,7 @@
       <c r="V557">
         <v>79335</v>
       </c>
-      <c r="W557">
+      <c r="W557" s="1">
         <v>79335</v>
       </c>
     </row>
@@ -42529,7 +42556,7 @@
       <c r="V558">
         <v>-67000</v>
       </c>
-      <c r="W558">
+      <c r="W558" s="1">
         <v>-67000</v>
       </c>
     </row>
@@ -42600,7 +42627,7 @@
       <c r="V559">
         <v>-4000</v>
       </c>
-      <c r="W559">
+      <c r="W559" s="1">
         <v>-4000</v>
       </c>
     </row>
@@ -42671,7 +42698,7 @@
       <c r="V560">
         <v>50</v>
       </c>
-      <c r="W560">
+      <c r="W560" s="1">
         <v>50</v>
       </c>
     </row>
@@ -42742,7 +42769,7 @@
       <c r="V561">
         <v>54100</v>
       </c>
-      <c r="W561">
+      <c r="W561" s="1">
         <v>54100</v>
       </c>
     </row>
@@ -42813,7 +42840,7 @@
       <c r="V562">
         <v>-3757</v>
       </c>
-      <c r="W562">
+      <c r="W562" s="1">
         <v>-3757</v>
       </c>
     </row>
@@ -42884,7 +42911,7 @@
       <c r="V563">
         <v>-69001</v>
       </c>
-      <c r="W563">
+      <c r="W563" s="1">
         <v>-69001</v>
       </c>
     </row>
@@ -42955,7 +42982,7 @@
       <c r="V564">
         <v>64</v>
       </c>
-      <c r="W564">
+      <c r="W564" s="1">
         <v>64</v>
       </c>
     </row>
@@ -43026,7 +43053,7 @@
       <c r="V565">
         <v>0</v>
       </c>
-      <c r="W565">
+      <c r="W565" s="1">
         <v>0</v>
       </c>
     </row>
@@ -43097,7 +43124,7 @@
       <c r="V566">
         <v>0</v>
       </c>
-      <c r="W566">
+      <c r="W566" s="1">
         <v>0</v>
       </c>
     </row>
@@ -43168,7 +43195,7 @@
       <c r="V567">
         <v>-2250</v>
       </c>
-      <c r="W567">
+      <c r="W567" s="1">
         <v>21750</v>
       </c>
     </row>
@@ -43239,7 +43266,7 @@
       <c r="V568">
         <v>-140000</v>
       </c>
-      <c r="W568">
+      <c r="W568" s="1">
         <v>0</v>
       </c>
     </row>
@@ -43310,7 +43337,7 @@
       <c r="V569">
         <v>149583</v>
       </c>
-      <c r="W569">
+      <c r="W569" s="1">
         <v>149583</v>
       </c>
     </row>
@@ -43381,7 +43408,7 @@
       <c r="V570">
         <v>0</v>
       </c>
-      <c r="W570">
+      <c r="W570" s="1">
         <v>0</v>
       </c>
     </row>
@@ -43452,7 +43479,7 @@
       <c r="V571">
         <v>82866</v>
       </c>
-      <c r="W571">
+      <c r="W571" s="1">
         <v>82866</v>
       </c>
     </row>
